--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B67904-E38E-4E54-BEAF-7343EB4B7F3C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54BEDD5-ADB6-4A5A-A1AF-E14539A3846C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="42">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -526,7 +526,7 @@
     <col min="3" max="3" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
     </row>
     <row r="3" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
@@ -592,7 +592,9 @@
       <c r="H4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="9"/>
+      <c r="I4" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
@@ -622,7 +624,9 @@
       <c r="H5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="9"/>
+      <c r="I5" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
@@ -652,7 +656,9 @@
       <c r="H6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="9"/>
+      <c r="I6" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
@@ -682,7 +688,9 @@
       <c r="H7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I7" s="9"/>
+      <c r="I7" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
@@ -712,7 +720,9 @@
       <c r="H8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="9"/>
+      <c r="I8" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
@@ -742,7 +752,9 @@
       <c r="H9" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I9" s="9"/>
+      <c r="I9" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
@@ -772,7 +784,9 @@
       <c r="H10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="9"/>
+      <c r="I10" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
@@ -802,7 +816,9 @@
       <c r="H11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="9"/>
+      <c r="I11" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
@@ -832,7 +848,9 @@
       <c r="H12" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I12" s="9"/>
+      <c r="I12" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
@@ -862,7 +880,9 @@
       <c r="H13" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I13" s="9"/>
+      <c r="I13" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
@@ -892,7 +912,9 @@
       <c r="H14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="9"/>
+      <c r="I14" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
@@ -922,7 +944,9 @@
       <c r="H15" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I15" s="9"/>
+      <c r="I15" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
@@ -952,7 +976,9 @@
       <c r="H16" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I16" s="9"/>
+      <c r="I16" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
@@ -982,7 +1008,9 @@
       <c r="H17" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I17" s="9"/>
+      <c r="I17" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
@@ -1012,7 +1040,9 @@
       <c r="H18" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I18" s="9"/>
+      <c r="I18" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
@@ -1042,7 +1072,9 @@
       <c r="H19" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I19" s="9"/>
+      <c r="I19" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
@@ -1072,7 +1104,9 @@
       <c r="H20" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="9"/>
+      <c r="I20" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
@@ -1102,7 +1136,9 @@
       <c r="H21" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I21" s="9"/>
+      <c r="I21" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
@@ -1132,7 +1168,9 @@
       <c r="H22" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I22" s="9"/>
+      <c r="I22" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
@@ -1162,7 +1200,9 @@
       <c r="H23" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I23" s="9"/>
+      <c r="I23" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
@@ -1192,7 +1232,9 @@
       <c r="H24" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I24" s="9"/>
+      <c r="I24" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
@@ -1222,7 +1264,9 @@
       <c r="H25" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I25" s="9"/>
+      <c r="I25" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
@@ -1252,7 +1296,9 @@
       <c r="H26" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I26" s="9"/>
+      <c r="I26" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
@@ -1282,7 +1328,9 @@
       <c r="H27" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I27" s="9"/>
+      <c r="I27" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
@@ -1312,7 +1360,9 @@
       <c r="H28" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I28" s="9"/>
+      <c r="I28" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
@@ -1342,7 +1392,9 @@
       <c r="H29" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I29" s="9"/>
+      <c r="I29" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
@@ -1372,7 +1424,9 @@
       <c r="H30" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I30" s="9"/>
+      <c r="I30" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
@@ -1402,7 +1456,9 @@
       <c r="H31" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I31" s="9"/>
+      <c r="I31" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
@@ -1432,7 +1488,9 @@
       <c r="H32" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I32" s="9"/>
+      <c r="I32" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
@@ -1462,7 +1520,9 @@
       <c r="H33" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I33" s="9"/>
+      <c r="I33" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
@@ -1492,7 +1552,9 @@
       <c r="H34" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I34" s="9"/>
+      <c r="I34" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54BEDD5-ADB6-4A5A-A1AF-E14539A3846C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70370009-391B-41F4-8C25-15CB1B186BE8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Attendance" sheetId="1" r:id="rId1"/>
+    <sheet name="SW_status" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="43">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -146,6 +147,9 @@
   </si>
   <si>
     <t>Mentor Name</t>
+  </si>
+  <si>
+    <t>UID</t>
   </si>
 </sst>
 </file>
@@ -155,7 +159,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -196,6 +200,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -205,7 +215,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -274,11 +284,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -299,6 +339,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1563,4 +1609,1117 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
+  <dimension ref="A3:L34"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="6">
+        <v>45019</v>
+      </c>
+      <c r="I3" s="6">
+        <v>45020</v>
+      </c>
+      <c r="J3" s="6">
+        <v>45021</v>
+      </c>
+      <c r="K3" s="6">
+        <v>45022</v>
+      </c>
+      <c r="L3" s="6">
+        <v>45023</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="11">
+        <v>248774</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+    </row>
+    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="12">
+        <v>249547</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+    </row>
+    <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>3</v>
+      </c>
+      <c r="B6" s="12">
+        <v>248825</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+    </row>
+    <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>4</v>
+      </c>
+      <c r="B7" s="12">
+        <v>249532</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+    </row>
+    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="12">
+        <v>249529</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+    </row>
+    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>6</v>
+      </c>
+      <c r="B9" s="12">
+        <v>248764</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+    </row>
+    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="12">
+        <v>248819</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+    </row>
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>8</v>
+      </c>
+      <c r="B11" s="12">
+        <v>248727</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+    </row>
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>9</v>
+      </c>
+      <c r="B12" s="12">
+        <v>248719</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+    </row>
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>10</v>
+      </c>
+      <c r="B13" s="12">
+        <v>248803</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>11</v>
+      </c>
+      <c r="B14" s="12">
+        <v>248793</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+    </row>
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>12</v>
+      </c>
+      <c r="B15" s="12">
+        <v>248735</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+    </row>
+    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>13</v>
+      </c>
+      <c r="B16" s="12">
+        <v>248722</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12">
+        <v>248734</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>15</v>
+      </c>
+      <c r="B18" s="12">
+        <v>248730</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+    </row>
+    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <v>16</v>
+      </c>
+      <c r="B19" s="12">
+        <v>248761</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+    </row>
+    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>17</v>
+      </c>
+      <c r="B20" s="12">
+        <v>249440</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+    </row>
+    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>18</v>
+      </c>
+      <c r="B21" s="12">
+        <v>248726</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+    </row>
+    <row r="22" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>19</v>
+      </c>
+      <c r="B22" s="12">
+        <v>249528</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
+        <v>20</v>
+      </c>
+      <c r="B23" s="12">
+        <v>248750</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+    </row>
+    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>21</v>
+      </c>
+      <c r="B24" s="12">
+        <v>248789</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+    </row>
+    <row r="25" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
+        <v>22</v>
+      </c>
+      <c r="B25" s="12">
+        <v>248769</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+    </row>
+    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>23</v>
+      </c>
+      <c r="B26" s="12">
+        <v>248765</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+    </row>
+    <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>24</v>
+      </c>
+      <c r="B27" s="12">
+        <v>248738</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+    </row>
+    <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>25</v>
+      </c>
+      <c r="B28" s="12">
+        <v>248792</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+    </row>
+    <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
+        <v>26</v>
+      </c>
+      <c r="B29" s="12">
+        <v>248737</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+    </row>
+    <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>27</v>
+      </c>
+      <c r="B30" s="12">
+        <v>249581</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+    </row>
+    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
+        <v>28</v>
+      </c>
+      <c r="B31" s="12">
+        <v>248777</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+    </row>
+    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
+        <v>29</v>
+      </c>
+      <c r="B32" s="12">
+        <v>248799</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+    </row>
+    <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
+        <v>30</v>
+      </c>
+      <c r="B33" s="12">
+        <v>248771</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+    </row>
+    <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
+        <v>31</v>
+      </c>
+      <c r="B34" s="12">
+        <v>248753</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70370009-391B-41F4-8C25-15CB1B186BE8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66861E60-6493-47FB-9DA6-12D744EAA471}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="43">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1696,7 +1696,9 @@
       <c r="J4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="9"/>
+      <c r="K4" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1730,7 +1732,9 @@
       <c r="J5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="9"/>
+      <c r="K5" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L5" s="9"/>
     </row>
     <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1764,7 +1768,9 @@
       <c r="J6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="9"/>
+      <c r="K6" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L6" s="9"/>
     </row>
     <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1798,7 +1804,9 @@
       <c r="J7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="9"/>
+      <c r="K7" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L7" s="9"/>
     </row>
     <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1832,7 +1840,9 @@
       <c r="J8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="9"/>
+      <c r="K8" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L8" s="9"/>
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1866,7 +1876,9 @@
       <c r="J9" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="9"/>
+      <c r="K9" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L9" s="9"/>
     </row>
     <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1900,7 +1912,9 @@
       <c r="J10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K10" s="9"/>
+      <c r="K10" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L10" s="9"/>
     </row>
     <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1934,7 +1948,9 @@
       <c r="J11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K11" s="9"/>
+      <c r="K11" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L11" s="9"/>
     </row>
     <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1968,7 +1984,9 @@
       <c r="J12" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="9"/>
+      <c r="K12" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L12" s="9"/>
     </row>
     <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2002,7 +2020,9 @@
       <c r="J13" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K13" s="9"/>
+      <c r="K13" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L13" s="9"/>
     </row>
     <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2036,7 +2056,9 @@
       <c r="J14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="9"/>
+      <c r="K14" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L14" s="9"/>
     </row>
     <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2070,7 +2092,9 @@
       <c r="J15" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="9"/>
+      <c r="K15" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L15" s="9"/>
     </row>
     <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2104,7 +2128,9 @@
       <c r="J16" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K16" s="9"/>
+      <c r="K16" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L16" s="9"/>
     </row>
     <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2138,7 +2164,9 @@
       <c r="J17" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K17" s="9"/>
+      <c r="K17" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L17" s="9"/>
     </row>
     <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2172,7 +2200,9 @@
       <c r="J18" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="9"/>
+      <c r="K18" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L18" s="9"/>
     </row>
     <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2206,7 +2236,9 @@
       <c r="J19" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K19" s="9"/>
+      <c r="K19" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L19" s="9"/>
     </row>
     <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2240,7 +2272,9 @@
       <c r="J20" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="9"/>
+      <c r="K20" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L20" s="9"/>
     </row>
     <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2274,7 +2308,9 @@
       <c r="J21" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K21" s="9"/>
+      <c r="K21" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L21" s="9"/>
     </row>
     <row r="22" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2308,7 +2344,9 @@
       <c r="J22" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="9"/>
+      <c r="K22" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L22" s="9"/>
     </row>
     <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2342,7 +2380,9 @@
       <c r="J23" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K23" s="9"/>
+      <c r="K23" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L23" s="9"/>
     </row>
     <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2376,7 +2416,9 @@
       <c r="J24" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K24" s="9"/>
+      <c r="K24" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L24" s="9"/>
     </row>
     <row r="25" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2410,7 +2452,9 @@
       <c r="J25" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K25" s="9"/>
+      <c r="K25" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L25" s="9"/>
     </row>
     <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2444,7 +2488,9 @@
       <c r="J26" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K26" s="9"/>
+      <c r="K26" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L26" s="9"/>
     </row>
     <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2478,7 +2524,9 @@
       <c r="J27" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K27" s="9"/>
+      <c r="K27" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L27" s="9"/>
     </row>
     <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2512,7 +2560,9 @@
       <c r="J28" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K28" s="9"/>
+      <c r="K28" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L28" s="9"/>
     </row>
     <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2546,7 +2596,9 @@
       <c r="J29" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K29" s="9"/>
+      <c r="K29" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L29" s="9"/>
     </row>
     <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2580,7 +2632,9 @@
       <c r="J30" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K30" s="9"/>
+      <c r="K30" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L30" s="9"/>
     </row>
     <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2614,7 +2668,9 @@
       <c r="J31" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K31" s="9"/>
+      <c r="K31" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L31" s="9"/>
     </row>
     <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2648,7 +2704,9 @@
       <c r="J32" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="9"/>
+      <c r="K32" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L32" s="9"/>
     </row>
     <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2682,7 +2740,9 @@
       <c r="J33" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K33" s="9"/>
+      <c r="K33" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L33" s="9"/>
     </row>
     <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2716,7 +2776,9 @@
       <c r="J34" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K34" s="9"/>
+      <c r="K34" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="L34" s="9"/>
     </row>
   </sheetData>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66861E60-6493-47FB-9DA6-12D744EAA471}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6B46A2-82B9-419C-A38C-F77936D362C8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="43">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1699,7 +1699,9 @@
       <c r="K4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="9"/>
+      <c r="L4" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
@@ -1735,7 +1737,9 @@
       <c r="K5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="9"/>
+      <c r="L5" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
@@ -1771,7 +1775,9 @@
       <c r="K6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="9"/>
+      <c r="L6" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
@@ -1807,7 +1813,9 @@
       <c r="K7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L7" s="9"/>
+      <c r="L7" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
@@ -1843,7 +1851,9 @@
       <c r="K8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L8" s="9"/>
+      <c r="L8" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
@@ -1879,7 +1889,9 @@
       <c r="K9" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="9"/>
+      <c r="L9" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
@@ -1915,7 +1927,9 @@
       <c r="K10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L10" s="9"/>
+      <c r="L10" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
@@ -1951,7 +1965,9 @@
       <c r="K11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L11" s="9"/>
+      <c r="L11" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
@@ -1987,7 +2003,9 @@
       <c r="K12" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="9"/>
+      <c r="L12" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
@@ -2023,7 +2041,9 @@
       <c r="K13" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L13" s="9"/>
+      <c r="L13" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
@@ -2059,7 +2079,9 @@
       <c r="K14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="9"/>
+      <c r="L14" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
@@ -2095,7 +2117,9 @@
       <c r="K15" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L15" s="9"/>
+      <c r="L15" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
@@ -2131,7 +2155,9 @@
       <c r="K16" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L16" s="9"/>
+      <c r="L16" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
@@ -2167,7 +2193,9 @@
       <c r="K17" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L17" s="9"/>
+      <c r="L17" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
@@ -2203,7 +2231,9 @@
       <c r="K18" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L18" s="9"/>
+      <c r="L18" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
@@ -2239,7 +2269,9 @@
       <c r="K19" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L19" s="9"/>
+      <c r="L19" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
@@ -2275,7 +2307,9 @@
       <c r="K20" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="9"/>
+      <c r="L20" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
@@ -2311,7 +2345,9 @@
       <c r="K21" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L21" s="9"/>
+      <c r="L21" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="22" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
@@ -2347,7 +2383,9 @@
       <c r="K22" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="9"/>
+      <c r="L22" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
@@ -2383,7 +2421,9 @@
       <c r="K23" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L23" s="9"/>
+      <c r="L23" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
@@ -2419,7 +2459,9 @@
       <c r="K24" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="9"/>
+      <c r="L24" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="25" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
@@ -2455,7 +2497,9 @@
       <c r="K25" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L25" s="9"/>
+      <c r="L25" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
@@ -2491,7 +2535,9 @@
       <c r="K26" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L26" s="9"/>
+      <c r="L26" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
@@ -2527,7 +2573,9 @@
       <c r="K27" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L27" s="9"/>
+      <c r="L27" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
@@ -2563,7 +2611,9 @@
       <c r="K28" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L28" s="9"/>
+      <c r="L28" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
@@ -2599,7 +2649,9 @@
       <c r="K29" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L29" s="9"/>
+      <c r="L29" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
@@ -2635,7 +2687,9 @@
       <c r="K30" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L30" s="9"/>
+      <c r="L30" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
@@ -2671,7 +2725,9 @@
       <c r="K31" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L31" s="9"/>
+      <c r="L31" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
@@ -2707,7 +2763,9 @@
       <c r="K32" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="9"/>
+      <c r="L32" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
@@ -2743,7 +2801,9 @@
       <c r="K33" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L33" s="9"/>
+      <c r="L33" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
@@ -2779,7 +2839,9 @@
       <c r="K34" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L34" s="9"/>
+      <c r="L34" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6B46A2-82B9-419C-A38C-F77936D362C8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70CC95D-725E-401B-8801-9F6A5FFF708D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="43">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1613,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:L34"/>
+  <dimension ref="A3:M34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1625,9 +1625,10 @@
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>36</v>
       </c>
@@ -1664,8 +1665,11 @@
       <c r="L3" s="6">
         <v>45023</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M3" s="6">
+        <v>45026</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1702,8 +1706,11 @@
       <c r="L4" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M4" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1740,8 +1747,11 @@
       <c r="L5" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M5" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1778,8 +1788,11 @@
       <c r="L6" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M6" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1816,8 +1829,11 @@
       <c r="L7" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1854,8 +1870,11 @@
       <c r="L8" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M8" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1892,8 +1911,11 @@
       <c r="L9" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M9" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1930,8 +1952,11 @@
       <c r="L10" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M10" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1968,8 +1993,11 @@
       <c r="L11" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M11" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -2006,8 +2034,11 @@
       <c r="L12" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M12" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -2044,8 +2075,11 @@
       <c r="L13" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M13" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -2082,8 +2116,11 @@
       <c r="L14" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M14" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2120,8 +2157,11 @@
       <c r="L15" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M15" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -2158,8 +2198,11 @@
       <c r="L16" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M16" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -2196,8 +2239,11 @@
       <c r="L17" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M17" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -2234,8 +2280,11 @@
       <c r="L18" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M18" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -2272,8 +2321,11 @@
       <c r="L19" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M19" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -2310,8 +2362,11 @@
       <c r="L20" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M20" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -2348,8 +2403,11 @@
       <c r="L21" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M21" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -2386,8 +2444,11 @@
       <c r="L22" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M22" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -2424,8 +2485,11 @@
       <c r="L23" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M23" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -2462,8 +2526,11 @@
       <c r="L24" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M24" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -2500,8 +2567,11 @@
       <c r="L25" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M25" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -2538,8 +2608,11 @@
       <c r="L26" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M26" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -2576,8 +2649,11 @@
       <c r="L27" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M27" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -2614,8 +2690,11 @@
       <c r="L28" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M28" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -2652,8 +2731,11 @@
       <c r="L29" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M29" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -2690,8 +2772,11 @@
       <c r="L30" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M30" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -2728,8 +2813,11 @@
       <c r="L31" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M31" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -2766,8 +2854,11 @@
       <c r="L32" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M32" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -2804,8 +2895,11 @@
       <c r="L33" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M33" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -2840,6 +2934,9 @@
         <v>5</v>
       </c>
       <c r="L34" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="M34" s="10" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70CC95D-725E-401B-8801-9F6A5FFF708D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7DAD81-DF67-4110-A580-62B5113639B4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,44 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Jagadees waran</author>
+  </authors>
+  <commentList>
+    <comment ref="M7" authorId="0" shapeId="0" xr:uid="{FF58AAAC-6CB5-458E-94E6-DCDAA03EC50C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>9:01</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M13" authorId="0" shapeId="0" xr:uid="{E89D8088-47A4-4D78-A444-FB2A8C402409}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>9:01</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="43">
   <si>
@@ -159,7 +197,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -205,6 +243,13 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1612,8 +1657,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:M34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
+  <dimension ref="A3:N34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1626,9 +1671,10 @@
     <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>36</v>
       </c>
@@ -1668,8 +1714,11 @@
       <c r="M3" s="6">
         <v>45026</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N3" s="6">
+        <v>44996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1709,8 +1758,9 @@
       <c r="M4" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N4" s="10"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1750,8 +1800,9 @@
       <c r="M5" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N5" s="10"/>
+    </row>
+    <row r="6" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1791,8 +1842,9 @@
       <c r="M6" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N6" s="10"/>
+    </row>
+    <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1832,8 +1884,9 @@
       <c r="M7" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N7" s="10"/>
+    </row>
+    <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1873,8 +1926,9 @@
       <c r="M8" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N8" s="10"/>
+    </row>
+    <row r="9" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1914,8 +1968,9 @@
       <c r="M9" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N9" s="10"/>
+    </row>
+    <row r="10" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1955,8 +2010,9 @@
       <c r="M10" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N10" s="10"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1996,8 +2052,9 @@
       <c r="M11" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N11" s="10"/>
+    </row>
+    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -2037,8 +2094,9 @@
       <c r="M12" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N12" s="10"/>
+    </row>
+    <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -2078,8 +2136,9 @@
       <c r="M13" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N13" s="10"/>
+    </row>
+    <row r="14" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -2119,8 +2178,9 @@
       <c r="M14" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N14" s="10"/>
+    </row>
+    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2160,8 +2220,9 @@
       <c r="M15" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N15" s="10"/>
+    </row>
+    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -2201,8 +2262,9 @@
       <c r="M16" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N16" s="10"/>
+    </row>
+    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -2242,8 +2304,9 @@
       <c r="M17" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N17" s="10"/>
+    </row>
+    <row r="18" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -2283,8 +2346,9 @@
       <c r="M18" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N18" s="10"/>
+    </row>
+    <row r="19" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -2324,8 +2388,9 @@
       <c r="M19" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N19" s="10"/>
+    </row>
+    <row r="20" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -2365,8 +2430,9 @@
       <c r="M20" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N20" s="10"/>
+    </row>
+    <row r="21" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -2406,8 +2472,9 @@
       <c r="M21" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N21" s="10"/>
+    </row>
+    <row r="22" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -2447,8 +2514,9 @@
       <c r="M22" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N22" s="10"/>
+    </row>
+    <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -2488,8 +2556,9 @@
       <c r="M23" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N23" s="10"/>
+    </row>
+    <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -2529,8 +2598,9 @@
       <c r="M24" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N24" s="10"/>
+    </row>
+    <row r="25" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -2570,8 +2640,9 @@
       <c r="M25" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N25" s="10"/>
+    </row>
+    <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -2611,8 +2682,9 @@
       <c r="M26" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N26" s="10"/>
+    </row>
+    <row r="27" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -2652,8 +2724,9 @@
       <c r="M27" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N27" s="10"/>
+    </row>
+    <row r="28" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -2693,8 +2766,9 @@
       <c r="M28" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N28" s="10"/>
+    </row>
+    <row r="29" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -2734,8 +2808,9 @@
       <c r="M29" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N29" s="10"/>
+    </row>
+    <row r="30" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -2775,8 +2850,9 @@
       <c r="M30" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N30" s="10"/>
+    </row>
+    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -2816,8 +2892,9 @@
       <c r="M31" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N31" s="10"/>
+    </row>
+    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -2857,8 +2934,9 @@
       <c r="M32" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N32" s="10"/>
+    </row>
+    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -2898,8 +2976,9 @@
       <c r="M33" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N33" s="10"/>
+    </row>
+    <row r="34" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -2939,8 +3018,10 @@
       <c r="M34" s="10" t="s">
         <v>5</v>
       </c>
+      <c r="N34" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7DAD81-DF67-4110-A580-62B5113639B4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979CFFD4-7ACA-4618-A841-82969774BE46}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <author>Jagadees waran</author>
   </authors>
   <commentList>
-    <comment ref="M7" authorId="0" shapeId="0" xr:uid="{FF58AAAC-6CB5-458E-94E6-DCDAA03EC50C}">
+    <comment ref="N7" authorId="0" shapeId="0" xr:uid="{F6F4F720-DA46-4DC0-8124-2D3953156CC6}">
       <text>
         <r>
           <rPr>
@@ -40,7 +40,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M13" authorId="0" shapeId="0" xr:uid="{E89D8088-47A4-4D78-A444-FB2A8C402409}">
+    <comment ref="N13" authorId="0" shapeId="0" xr:uid="{FDBC7F03-2036-496C-8DA4-E2730B6FDC9C}">
       <text>
         <r>
           <rPr>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -188,6 +188,9 @@
   </si>
   <si>
     <t>UID</t>
+  </si>
+  <si>
+    <t>Jagadeeswaran</t>
   </si>
 </sst>
 </file>
@@ -1658,7 +1661,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:N34"/>
+  <dimension ref="A3:O34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1672,9 +1675,10 @@
     <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:14" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>36</v>
       </c>
@@ -1717,8 +1721,11 @@
       <c r="N3" s="6">
         <v>44996</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O3" s="6">
+        <v>45028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1735,7 +1742,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>4</v>
@@ -1758,9 +1765,14 @@
       <c r="M4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="10"/>
-    </row>
-    <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1777,7 +1789,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>4</v>
@@ -1800,9 +1812,14 @@
       <c r="M5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N5" s="10"/>
-    </row>
-    <row r="6" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1819,7 +1836,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>4</v>
@@ -1842,9 +1859,14 @@
       <c r="M6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="10"/>
-    </row>
-    <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1861,7 +1883,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>4</v>
@@ -1884,9 +1906,14 @@
       <c r="M7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="10"/>
-    </row>
-    <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1903,7 +1930,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>4</v>
@@ -1926,9 +1953,14 @@
       <c r="M8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N8" s="10"/>
-    </row>
-    <row r="9" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1945,7 +1977,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>4</v>
@@ -1968,9 +2000,14 @@
       <c r="M9" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N9" s="10"/>
-    </row>
-    <row r="10" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1987,7 +2024,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>4</v>
@@ -2010,9 +2047,14 @@
       <c r="M10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N10" s="10"/>
-    </row>
-    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N10" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -2029,7 +2071,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>4</v>
@@ -2052,9 +2094,14 @@
       <c r="M11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N11" s="10"/>
-    </row>
-    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O11" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -2071,7 +2118,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>4</v>
@@ -2094,9 +2141,14 @@
       <c r="M12" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="10"/>
-    </row>
-    <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O12" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -2113,7 +2165,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>4</v>
@@ -2136,9 +2188,14 @@
       <c r="M13" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N13" s="10"/>
-    </row>
-    <row r="14" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O13" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -2155,7 +2212,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>4</v>
@@ -2178,9 +2235,14 @@
       <c r="M14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="10"/>
-    </row>
-    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N14" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2197,7 +2259,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>4</v>
@@ -2220,9 +2282,14 @@
       <c r="M15" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N15" s="10"/>
-    </row>
-    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N15" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -2239,7 +2306,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>4</v>
@@ -2262,9 +2329,14 @@
       <c r="M16" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N16" s="10"/>
-    </row>
-    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N16" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O16" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -2281,7 +2353,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>4</v>
@@ -2304,9 +2376,14 @@
       <c r="M17" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N17" s="10"/>
-    </row>
-    <row r="18" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N17" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -2323,7 +2400,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>4</v>
@@ -2346,9 +2423,14 @@
       <c r="M18" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N18" s="10"/>
-    </row>
-    <row r="19" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N18" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -2365,7 +2447,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>4</v>
@@ -2388,9 +2470,14 @@
       <c r="M19" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N19" s="10"/>
-    </row>
-    <row r="20" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N19" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O19" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -2407,7 +2494,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>4</v>
@@ -2430,9 +2517,14 @@
       <c r="M20" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N20" s="10"/>
-    </row>
-    <row r="21" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N20" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O20" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -2449,7 +2541,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>4</v>
@@ -2472,9 +2564,14 @@
       <c r="M21" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N21" s="10"/>
-    </row>
-    <row r="22" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N21" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -2491,7 +2588,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>4</v>
@@ -2514,9 +2611,14 @@
       <c r="M22" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="10"/>
-    </row>
-    <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N22" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -2533,7 +2635,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>4</v>
@@ -2556,9 +2658,14 @@
       <c r="M23" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N23" s="10"/>
-    </row>
-    <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N23" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -2575,7 +2682,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>4</v>
@@ -2598,9 +2705,14 @@
       <c r="M24" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N24" s="10"/>
-    </row>
-    <row r="25" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N24" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -2617,7 +2729,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>4</v>
@@ -2640,9 +2752,14 @@
       <c r="M25" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N25" s="10"/>
-    </row>
-    <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N25" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O25" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -2659,7 +2776,7 @@
         <v>2</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>4</v>
@@ -2682,9 +2799,14 @@
       <c r="M26" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N26" s="10"/>
-    </row>
-    <row r="27" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N26" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -2701,7 +2823,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>4</v>
@@ -2724,9 +2846,14 @@
       <c r="M27" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N27" s="10"/>
-    </row>
-    <row r="28" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N27" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -2743,7 +2870,7 @@
         <v>2</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>4</v>
@@ -2766,9 +2893,14 @@
       <c r="M28" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N28" s="10"/>
-    </row>
-    <row r="29" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N28" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O28" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -2785,7 +2917,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>4</v>
@@ -2808,9 +2940,14 @@
       <c r="M29" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N29" s="10"/>
-    </row>
-    <row r="30" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N29" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O29" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -2827,7 +2964,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>4</v>
@@ -2850,9 +2987,14 @@
       <c r="M30" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N30" s="10"/>
-    </row>
-    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N30" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O30" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -2869,7 +3011,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>4</v>
@@ -2892,9 +3034,14 @@
       <c r="M31" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N31" s="10"/>
-    </row>
-    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N31" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O31" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -2911,7 +3058,7 @@
         <v>2</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>4</v>
@@ -2934,9 +3081,14 @@
       <c r="M32" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N32" s="10"/>
-    </row>
-    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N32" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O32" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -2953,7 +3105,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>4</v>
@@ -2976,9 +3128,14 @@
       <c r="M33" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N33" s="10"/>
-    </row>
-    <row r="34" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N33" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O33" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -2995,7 +3152,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>4</v>
@@ -3018,7 +3175,12 @@
       <c r="M34" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N34" s="10"/>
+      <c r="N34" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O34" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979CFFD4-7ACA-4618-A841-82969774BE46}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEF40CC-5A20-489C-8271-E53E84297181}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1661,7 +1661,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:O34"/>
+  <dimension ref="A3:P34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1675,10 +1675,10 @@
     <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>36</v>
       </c>
@@ -1724,8 +1724,11 @@
       <c r="O3" s="6">
         <v>45028</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P3" s="6">
+        <v>45029</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1771,8 +1774,11 @@
       <c r="O4" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P4" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1818,8 +1824,11 @@
       <c r="O5" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P5" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1865,8 +1874,11 @@
       <c r="O6" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P6" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1912,8 +1924,11 @@
       <c r="O7" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P7" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1959,8 +1974,11 @@
       <c r="O8" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P8" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -2006,8 +2024,11 @@
       <c r="O9" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P9" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -2053,8 +2074,11 @@
       <c r="O10" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P10" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -2100,8 +2124,11 @@
       <c r="O11" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P11" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -2147,8 +2174,11 @@
       <c r="O12" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P12" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -2194,8 +2224,11 @@
       <c r="O13" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P13" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -2241,8 +2274,11 @@
       <c r="O14" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P14" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2288,8 +2324,11 @@
       <c r="O15" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P15" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -2335,8 +2374,11 @@
       <c r="O16" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P16" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -2382,8 +2424,11 @@
       <c r="O17" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P17" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -2429,8 +2474,11 @@
       <c r="O18" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P18" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -2476,8 +2524,11 @@
       <c r="O19" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P19" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -2523,8 +2574,11 @@
       <c r="O20" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P20" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -2570,8 +2624,11 @@
       <c r="O21" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P21" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -2617,8 +2674,11 @@
       <c r="O22" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P22" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -2664,8 +2724,11 @@
       <c r="O23" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P23" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -2711,8 +2774,11 @@
       <c r="O24" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P24" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -2758,8 +2824,11 @@
       <c r="O25" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P25" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -2805,8 +2874,11 @@
       <c r="O26" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P26" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -2852,8 +2924,11 @@
       <c r="O27" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P27" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -2899,8 +2974,11 @@
       <c r="O28" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P28" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -2946,8 +3024,11 @@
       <c r="O29" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P29" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -2993,8 +3074,11 @@
       <c r="O30" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P30" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -3040,8 +3124,11 @@
       <c r="O31" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P31" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -3087,8 +3174,11 @@
       <c r="O32" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P32" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -3134,8 +3224,11 @@
       <c r="O33" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P33" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -3179,6 +3272,9 @@
         <v>5</v>
       </c>
       <c r="O34" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="P34" s="10" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEF40CC-5A20-489C-8271-E53E84297181}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD8C63E-C109-4537-9337-459B3825DC89}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1661,7 +1661,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:P34"/>
+  <dimension ref="A3:Q34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1675,10 +1675,10 @@
     <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>36</v>
       </c>
@@ -1727,8 +1727,11 @@
       <c r="P3" s="6">
         <v>45029</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q3" s="6">
+        <v>45030</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1777,8 +1780,11 @@
       <c r="P4" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q4" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1827,8 +1833,11 @@
       <c r="P5" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q5" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1877,8 +1886,11 @@
       <c r="P6" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q6" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1927,8 +1939,11 @@
       <c r="P7" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q7" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1977,8 +1992,11 @@
       <c r="P8" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q8" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -2027,8 +2045,11 @@
       <c r="P9" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q9" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -2077,8 +2098,11 @@
       <c r="P10" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q10" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -2127,8 +2151,11 @@
       <c r="P11" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q11" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -2177,8 +2204,11 @@
       <c r="P12" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q12" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -2227,8 +2257,11 @@
       <c r="P13" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q13" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -2277,8 +2310,11 @@
       <c r="P14" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q14" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2327,8 +2363,11 @@
       <c r="P15" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q15" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -2377,8 +2416,11 @@
       <c r="P16" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q16" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -2427,8 +2469,11 @@
       <c r="P17" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q17" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -2477,8 +2522,11 @@
       <c r="P18" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q18" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -2527,8 +2575,11 @@
       <c r="P19" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q19" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -2577,8 +2628,11 @@
       <c r="P20" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q20" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -2627,8 +2681,11 @@
       <c r="P21" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q21" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -2677,8 +2734,11 @@
       <c r="P22" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q22" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -2727,8 +2787,11 @@
       <c r="P23" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q23" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -2777,8 +2840,11 @@
       <c r="P24" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q24" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -2827,8 +2893,11 @@
       <c r="P25" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q25" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -2877,8 +2946,11 @@
       <c r="P26" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q26" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -2927,8 +2999,11 @@
       <c r="P27" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q27" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -2977,8 +3052,11 @@
       <c r="P28" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q28" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -3027,8 +3105,11 @@
       <c r="P29" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q29" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -3077,8 +3158,11 @@
       <c r="P30" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q30" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -3127,8 +3211,11 @@
       <c r="P31" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q31" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -3177,8 +3264,11 @@
       <c r="P32" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q32" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -3227,8 +3317,11 @@
       <c r="P33" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q33" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -3275,6 +3368,9 @@
         <v>5</v>
       </c>
       <c r="P34" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="10" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD8C63E-C109-4537-9337-459B3825DC89}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE80102-DAE2-4DB9-BBDB-B43B9BFD10F5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,6 +26,20 @@
     <author>Jagadees waran</author>
   </authors>
   <commentList>
+    <comment ref="R5" authorId="0" shapeId="0" xr:uid="{8BF2E323-DE32-4CE1-A9CC-13BC49B58B9C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>9:02</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="N7" authorId="0" shapeId="0" xr:uid="{F6F4F720-DA46-4DC0-8124-2D3953156CC6}">
       <text>
         <r>
@@ -54,12 +68,40 @@
         </r>
       </text>
     </comment>
+    <comment ref="R25" authorId="0" shapeId="0" xr:uid="{2E3360AC-93ED-47D5-A29A-768ED91910D3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>9:02</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R29" authorId="0" shapeId="0" xr:uid="{80A47C8C-A3F5-499A-B36F-2D635D4CE47A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>9:02</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="45">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -191,6 +233,9 @@
   </si>
   <si>
     <t>Jagadeeswaran</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -1661,7 +1706,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:Q34"/>
+  <dimension ref="A3:R34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1675,10 +1720,10 @@
     <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>36</v>
       </c>
@@ -1730,8 +1775,11 @@
       <c r="Q3" s="6">
         <v>45030</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R3" s="6">
+        <v>45033</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1783,8 +1831,11 @@
       <c r="Q4" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R4" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1836,8 +1887,11 @@
       <c r="Q5" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R5" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1889,8 +1943,11 @@
       <c r="Q6" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R6" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1942,8 +1999,11 @@
       <c r="Q7" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R7" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1995,8 +2055,11 @@
       <c r="Q8" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R8" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -2048,8 +2111,11 @@
       <c r="Q9" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R9" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -2101,8 +2167,11 @@
       <c r="Q10" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R10" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -2154,8 +2223,11 @@
       <c r="Q11" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R11" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -2207,8 +2279,11 @@
       <c r="Q12" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R12" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -2260,8 +2335,11 @@
       <c r="Q13" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R13" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -2313,8 +2391,11 @@
       <c r="Q14" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R14" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2366,8 +2447,11 @@
       <c r="Q15" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R15" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -2419,8 +2503,11 @@
       <c r="Q16" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R16" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -2472,8 +2559,11 @@
       <c r="Q17" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R17" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -2525,8 +2615,11 @@
       <c r="Q18" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R18" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -2578,8 +2671,11 @@
       <c r="Q19" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R19" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -2631,8 +2727,11 @@
       <c r="Q20" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R20" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -2684,8 +2783,11 @@
       <c r="Q21" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R21" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -2737,8 +2839,11 @@
       <c r="Q22" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R22" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -2790,8 +2895,11 @@
       <c r="Q23" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R23" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -2843,8 +2951,11 @@
       <c r="Q24" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R24" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -2896,8 +3007,11 @@
       <c r="Q25" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R25" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -2949,8 +3063,11 @@
       <c r="Q26" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R26" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -3002,8 +3119,11 @@
       <c r="Q27" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R27" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -3055,8 +3175,11 @@
       <c r="Q28" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R28" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -3108,8 +3231,11 @@
       <c r="Q29" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R29" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -3161,8 +3287,11 @@
       <c r="Q30" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R30" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -3214,8 +3343,11 @@
       <c r="Q31" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R31" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -3267,8 +3399,11 @@
       <c r="Q32" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R32" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -3320,8 +3455,11 @@
       <c r="Q33" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R33" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -3371,6 +3509,9 @@
         <v>5</v>
       </c>
       <c r="Q34" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="R34" s="10" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE80102-DAE2-4DB9-BBDB-B43B9BFD10F5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBEB41E-0B89-41E2-BBC4-EA49ED8EF026}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="45">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1706,7 +1706,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:R34"/>
+  <dimension ref="A3:S34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1720,10 +1720,10 @@
     <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>36</v>
       </c>
@@ -1778,8 +1778,11 @@
       <c r="R3" s="6">
         <v>45033</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S3" s="6">
+        <v>45034</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1834,8 +1837,11 @@
       <c r="R4" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S4" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1890,8 +1896,11 @@
       <c r="R5" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S5" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1946,8 +1955,11 @@
       <c r="R6" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S6" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -2002,8 +2014,11 @@
       <c r="R7" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S7" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -2058,8 +2073,11 @@
       <c r="R8" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S8" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -2114,8 +2132,11 @@
       <c r="R9" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S9" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -2170,8 +2191,11 @@
       <c r="R10" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S10" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -2226,8 +2250,11 @@
       <c r="R11" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S11" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -2282,8 +2309,11 @@
       <c r="R12" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S12" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -2338,8 +2368,11 @@
       <c r="R13" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S13" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -2394,8 +2427,11 @@
       <c r="R14" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S14" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2450,8 +2486,11 @@
       <c r="R15" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S15" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -2506,8 +2545,11 @@
       <c r="R16" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S16" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -2562,8 +2604,11 @@
       <c r="R17" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S17" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -2618,8 +2663,11 @@
       <c r="R18" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S18" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -2674,8 +2722,11 @@
       <c r="R19" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S19" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -2730,8 +2781,11 @@
       <c r="R20" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S20" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -2786,8 +2840,11 @@
       <c r="R21" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S21" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -2842,8 +2899,11 @@
       <c r="R22" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S22" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -2898,8 +2958,11 @@
       <c r="R23" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S23" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -2954,8 +3017,11 @@
       <c r="R24" s="10" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S24" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -3010,8 +3076,11 @@
       <c r="R25" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S25" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -3066,8 +3135,11 @@
       <c r="R26" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S26" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -3122,8 +3194,11 @@
       <c r="R27" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S27" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -3178,8 +3253,11 @@
       <c r="R28" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S28" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -3234,8 +3312,11 @@
       <c r="R29" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S29" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -3290,8 +3371,11 @@
       <c r="R30" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S30" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -3346,8 +3430,11 @@
       <c r="R31" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S31" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -3402,8 +3489,11 @@
       <c r="R32" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S32" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -3458,8 +3548,11 @@
       <c r="R33" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S33" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -3512,6 +3605,9 @@
         <v>5</v>
       </c>
       <c r="R34" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="S34" s="10" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B0B58D-A725-4F1E-A09E-35E8F8D782A1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C472BEB1-44DF-49BF-8A9F-69BB1984FECE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="2" r:id="rId1"/>
@@ -67,6 +67,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="U13" authorId="0" shapeId="0" xr:uid="{1E8BE0D8-C445-4EC3-81D4-96F70D8C98B3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>9:04</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R25" authorId="0" shapeId="0" xr:uid="{2E3360AC-93ED-47D5-A29A-768ED91910D3}">
       <text>
         <r>
@@ -100,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -640,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:T34"/>
+  <dimension ref="A3:U34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -654,10 +668,10 @@
     <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="21" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -718,8 +732,11 @@
       <c r="T3" s="5">
         <v>45035</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U3" s="5">
+        <v>45036</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -780,8 +797,11 @@
       <c r="T4" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U4" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -842,8 +862,11 @@
       <c r="T5" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -904,8 +927,11 @@
       <c r="T6" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U6" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -966,8 +992,11 @@
       <c r="T7" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U7" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1028,8 +1057,11 @@
       <c r="T8" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U8" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1090,8 +1122,11 @@
       <c r="T9" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U9" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1152,8 +1187,11 @@
       <c r="T10" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U10" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1214,8 +1252,11 @@
       <c r="T11" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U11" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1276,8 +1317,11 @@
       <c r="T12" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U12" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1338,8 +1382,11 @@
       <c r="T13" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U13" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -1400,8 +1447,11 @@
       <c r="T14" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U14" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -1462,8 +1512,11 @@
       <c r="T15" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U15" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -1524,8 +1577,11 @@
       <c r="T16" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U16" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -1586,8 +1642,11 @@
       <c r="T17" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U17" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -1648,8 +1707,11 @@
       <c r="T18" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U18" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -1710,8 +1772,11 @@
       <c r="T19" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U19" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -1772,8 +1837,11 @@
       <c r="T20" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U20" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -1834,8 +1902,11 @@
       <c r="T21" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U21" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -1896,8 +1967,11 @@
       <c r="T22" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U22" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -1958,8 +2032,11 @@
       <c r="T23" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U23" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -2020,8 +2097,11 @@
       <c r="T24" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U24" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -2082,8 +2162,11 @@
       <c r="T25" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U25" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -2144,8 +2227,11 @@
       <c r="T26" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U26" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -2206,8 +2292,11 @@
       <c r="T27" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U27" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -2268,8 +2357,11 @@
       <c r="T28" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U28" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -2330,8 +2422,11 @@
       <c r="T29" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U29" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -2392,8 +2487,11 @@
       <c r="T30" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U30" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -2454,8 +2552,11 @@
       <c r="T31" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U31" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -2516,8 +2617,11 @@
       <c r="T32" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U32" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -2578,8 +2682,11 @@
       <c r="T33" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U33" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -2638,6 +2745,9 @@
         <v>4</v>
       </c>
       <c r="T34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="U34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C472BEB1-44DF-49BF-8A9F-69BB1984FECE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC83AD2-76A7-4267-8158-A66C8474C18F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="168" windowWidth="23016" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="2" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -654,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:U34"/>
+  <dimension ref="A3:V34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -668,10 +668,10 @@
     <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="21" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="22" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -735,8 +735,11 @@
       <c r="U3" s="5">
         <v>45036</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V3" s="5">
+        <v>45040</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -800,8 +803,11 @@
       <c r="U4" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V4" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -865,8 +871,11 @@
       <c r="U5" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -930,8 +939,11 @@
       <c r="U6" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V6" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -995,8 +1007,11 @@
       <c r="U7" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V7" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1060,8 +1075,11 @@
       <c r="U8" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V8" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1125,8 +1143,11 @@
       <c r="U9" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V9" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1190,8 +1211,11 @@
       <c r="U10" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V10" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1255,8 +1279,11 @@
       <c r="U11" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V11" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1320,8 +1347,11 @@
       <c r="U12" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V12" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1385,8 +1415,11 @@
       <c r="U13" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V13" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -1450,8 +1483,11 @@
       <c r="U14" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V14" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -1515,8 +1551,11 @@
       <c r="U15" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V15" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -1580,8 +1619,11 @@
       <c r="U16" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V16" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -1645,8 +1687,11 @@
       <c r="U17" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V17" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -1710,8 +1755,11 @@
       <c r="U18" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V18" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -1775,8 +1823,11 @@
       <c r="U19" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V19" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -1840,8 +1891,11 @@
       <c r="U20" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V20" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -1905,8 +1959,11 @@
       <c r="U21" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V21" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -1970,8 +2027,11 @@
       <c r="U22" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V22" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -2035,8 +2095,11 @@
       <c r="U23" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V23" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -2100,8 +2163,11 @@
       <c r="U24" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V24" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -2165,8 +2231,11 @@
       <c r="U25" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V25" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -2230,8 +2299,11 @@
       <c r="U26" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V26" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -2295,8 +2367,11 @@
       <c r="U27" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V27" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -2360,8 +2435,11 @@
       <c r="U28" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V28" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -2425,8 +2503,11 @@
       <c r="U29" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V29" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -2490,8 +2571,11 @@
       <c r="U30" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V30" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -2555,8 +2639,11 @@
       <c r="U31" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V31" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -2620,8 +2707,11 @@
       <c r="U32" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V32" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -2685,8 +2775,11 @@
       <c r="U33" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V33" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -2748,6 +2841,9 @@
         <v>4</v>
       </c>
       <c r="U34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="V34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC83AD2-76A7-4267-8158-A66C8474C18F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B6B439-E664-4508-AA37-322C0F531D42}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="168" windowWidth="23016" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="2" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -654,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:V34"/>
+  <dimension ref="A3:W34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -668,10 +668,10 @@
     <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="22" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="23" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:22" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -738,8 +738,11 @@
       <c r="V3" s="5">
         <v>45040</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W3" s="5">
+        <v>45041</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -806,8 +809,11 @@
       <c r="V4" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W4" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -874,8 +880,11 @@
       <c r="V5" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -942,8 +951,11 @@
       <c r="V6" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W6" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1010,8 +1022,11 @@
       <c r="V7" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W7" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1078,8 +1093,11 @@
       <c r="V8" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W8" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1146,8 +1164,11 @@
       <c r="V9" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W9" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1214,8 +1235,11 @@
       <c r="V10" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W10" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1282,8 +1306,11 @@
       <c r="V11" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W11" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1350,8 +1377,11 @@
       <c r="V12" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W12" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1418,8 +1448,11 @@
       <c r="V13" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W13" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -1486,8 +1519,11 @@
       <c r="V14" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W14" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -1554,8 +1590,11 @@
       <c r="V15" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W15" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -1622,8 +1661,11 @@
       <c r="V16" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W16" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -1690,8 +1732,11 @@
       <c r="V17" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W17" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -1758,8 +1803,11 @@
       <c r="V18" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W18" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -1826,8 +1874,11 @@
       <c r="V19" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W19" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -1894,8 +1945,11 @@
       <c r="V20" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W20" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -1962,8 +2016,11 @@
       <c r="V21" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W21" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -2030,8 +2087,11 @@
       <c r="V22" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W22" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -2098,8 +2158,11 @@
       <c r="V23" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W23" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -2166,8 +2229,11 @@
       <c r="V24" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W24" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -2234,8 +2300,11 @@
       <c r="V25" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W25" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -2302,8 +2371,11 @@
       <c r="V26" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W26" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -2370,8 +2442,11 @@
       <c r="V27" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W27" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -2438,8 +2513,11 @@
       <c r="V28" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W28" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -2506,8 +2584,11 @@
       <c r="V29" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W29" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -2574,8 +2655,11 @@
       <c r="V30" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W30" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -2642,8 +2726,11 @@
       <c r="V31" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W31" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -2710,8 +2797,11 @@
       <c r="V32" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W32" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -2778,8 +2868,11 @@
       <c r="V33" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W33" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -2844,6 +2937,9 @@
         <v>4</v>
       </c>
       <c r="V34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="W34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B6B439-E664-4508-AA37-322C0F531D42}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF292CC7-8FC8-4E75-B8DC-911FD403628F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,6 +81,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="X13" authorId="0" shapeId="0" xr:uid="{25E94228-3970-4057-8D26-EE7D8AB7BF1E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>9:04</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X20" authorId="0" shapeId="0" xr:uid="{DA902251-6155-45D0-BF90-7E5F5DFDE287}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>9:01</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R25" authorId="0" shapeId="0" xr:uid="{2E3360AC-93ED-47D5-A29A-768ED91910D3}">
       <text>
         <r>
@@ -114,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -654,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:W34"/>
+  <dimension ref="A3:X34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -668,10 +696,10 @@
     <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="23" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="24" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -741,8 +769,11 @@
       <c r="W3" s="5">
         <v>45041</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X3" s="5">
+        <v>45042</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -812,8 +843,11 @@
       <c r="W4" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X4" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -883,8 +917,11 @@
       <c r="W5" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -954,8 +991,11 @@
       <c r="W6" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X6" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1025,8 +1065,11 @@
       <c r="W7" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X7" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1096,8 +1139,11 @@
       <c r="W8" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X8" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1167,8 +1213,11 @@
       <c r="W9" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X9" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1238,8 +1287,11 @@
       <c r="W10" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X10" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1309,8 +1361,11 @@
       <c r="W11" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X11" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1380,8 +1435,11 @@
       <c r="W12" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X12" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1451,8 +1509,11 @@
       <c r="W13" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X13" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -1522,8 +1583,11 @@
       <c r="W14" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X14" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -1593,8 +1657,11 @@
       <c r="W15" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X15" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -1664,8 +1731,11 @@
       <c r="W16" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X16" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -1735,8 +1805,11 @@
       <c r="W17" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X17" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -1806,8 +1879,11 @@
       <c r="W18" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X18" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -1877,8 +1953,11 @@
       <c r="W19" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X19" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -1948,8 +2027,11 @@
       <c r="W20" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X20" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -2019,8 +2101,11 @@
       <c r="W21" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X21" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -2090,8 +2175,11 @@
       <c r="W22" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X22" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -2161,8 +2249,11 @@
       <c r="W23" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X23" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -2232,8 +2323,11 @@
       <c r="W24" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X24" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -2303,8 +2397,11 @@
       <c r="W25" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X25" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -2374,8 +2471,11 @@
       <c r="W26" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X26" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -2445,8 +2545,11 @@
       <c r="W27" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X27" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -2516,8 +2619,11 @@
       <c r="W28" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X28" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -2587,8 +2693,11 @@
       <c r="W29" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X29" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -2658,8 +2767,11 @@
       <c r="W30" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X30" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -2729,8 +2841,11 @@
       <c r="W31" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X31" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -2800,8 +2915,11 @@
       <c r="W32" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X32" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -2871,8 +2989,11 @@
       <c r="W33" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X33" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -2942,9 +3063,13 @@
       <c r="W34" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="X34" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF292CC7-8FC8-4E75-B8DC-911FD403628F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0016F1-1A5D-4902-8AD5-72BBD44E8D3C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -682,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:X34"/>
+  <dimension ref="A3:Y34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -696,10 +696,10 @@
     <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="24" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="25" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:24" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -772,8 +772,11 @@
       <c r="X3" s="5">
         <v>45042</v>
       </c>
+      <c r="Y3" s="5">
+        <v>45043</v>
+      </c>
     </row>
-    <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -846,8 +849,11 @@
       <c r="X4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -920,8 +926,11 @@
       <c r="X5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -994,8 +1003,11 @@
       <c r="X6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1068,8 +1080,11 @@
       <c r="X7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1142,8 +1157,11 @@
       <c r="X8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1216,8 +1234,11 @@
       <c r="X9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1290,8 +1311,11 @@
       <c r="X10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1364,8 +1388,11 @@
       <c r="X11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1438,8 +1465,11 @@
       <c r="X12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1512,8 +1542,11 @@
       <c r="X13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -1586,8 +1619,11 @@
       <c r="X14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -1660,8 +1696,11 @@
       <c r="X15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -1734,8 +1773,11 @@
       <c r="X16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -1808,8 +1850,11 @@
       <c r="X17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -1882,8 +1927,11 @@
       <c r="X18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -1956,8 +2004,11 @@
       <c r="X19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -2030,8 +2081,11 @@
       <c r="X20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -2104,8 +2158,11 @@
       <c r="X21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -2178,8 +2235,11 @@
       <c r="X22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -2252,8 +2312,11 @@
       <c r="X23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -2326,8 +2389,11 @@
       <c r="X24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -2400,8 +2466,11 @@
       <c r="X25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -2474,8 +2543,11 @@
       <c r="X26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -2548,8 +2620,11 @@
       <c r="X27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -2622,8 +2697,11 @@
       <c r="X28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -2696,8 +2774,11 @@
       <c r="X29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -2770,8 +2851,11 @@
       <c r="X30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -2844,8 +2928,11 @@
       <c r="X31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -2918,8 +3005,11 @@
       <c r="X32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -2992,8 +3082,11 @@
       <c r="X33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Y33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -3064,6 +3157,9 @@
         <v>4</v>
       </c>
       <c r="X34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0016F1-1A5D-4902-8AD5-72BBD44E8D3C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2398182-3E75-40AF-A18C-B5A9A76A47F5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,6 +95,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="Z18" authorId="0" shapeId="0" xr:uid="{08D2A270-552A-494A-8EB7-D7239F622756}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="X20" authorId="0" shapeId="0" xr:uid="{DA902251-6155-45D0-BF90-7E5F5DFDE287}">
       <text>
         <r>
@@ -106,6 +120,20 @@
             <charset val="1"/>
           </rPr>
           <t>9:01</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z22" authorId="0" shapeId="0" xr:uid="{DDD8C7AD-47C9-4E11-8FE8-07117ACB2789}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
         </r>
       </text>
     </comment>
@@ -137,12 +165,26 @@
         </r>
       </text>
     </comment>
+    <comment ref="Z32" authorId="0" shapeId="0" xr:uid="{59E0B9C2-F2EA-4082-81B3-59239B204C71}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -443,7 +485,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -467,6 +509,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -682,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:Y34"/>
+  <dimension ref="A3:AA34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -696,10 +739,10 @@
     <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="25" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="26" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -775,8 +818,11 @@
       <c r="Y3" s="5">
         <v>45043</v>
       </c>
+      <c r="Z3" s="5">
+        <v>45044</v>
+      </c>
     </row>
-    <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -852,8 +898,11 @@
       <c r="Y4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -929,8 +978,11 @@
       <c r="Y5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1006,8 +1058,11 @@
       <c r="Y6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1083,8 +1138,11 @@
       <c r="Y7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1160,8 +1218,11 @@
       <c r="Y8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1237,8 +1298,11 @@
       <c r="Y9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1314,8 +1378,11 @@
       <c r="Y10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1391,8 +1458,11 @@
       <c r="Y11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1468,8 +1538,11 @@
       <c r="Y12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1545,8 +1618,11 @@
       <c r="Y13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -1622,8 +1698,11 @@
       <c r="Y14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -1699,8 +1778,11 @@
       <c r="Y15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -1776,8 +1858,11 @@
       <c r="Y16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -1853,8 +1938,11 @@
       <c r="Y17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -1930,8 +2018,12 @@
       <c r="Y18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA18" s="11"/>
     </row>
-    <row r="19" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -2007,8 +2099,11 @@
       <c r="Y19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -2084,8 +2179,11 @@
       <c r="Y20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -2161,8 +2259,11 @@
       <c r="Y21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -2238,8 +2339,11 @@
       <c r="Y22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -2315,8 +2419,11 @@
       <c r="Y23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -2392,8 +2499,11 @@
       <c r="Y24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -2469,8 +2579,11 @@
       <c r="Y25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -2546,8 +2659,11 @@
       <c r="Y26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -2623,8 +2739,11 @@
       <c r="Y27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -2700,8 +2819,11 @@
       <c r="Y28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -2777,8 +2899,11 @@
       <c r="Y29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -2854,8 +2979,11 @@
       <c r="Y30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -2931,8 +3059,11 @@
       <c r="Y31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -3008,8 +3139,11 @@
       <c r="Y32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -3085,8 +3219,11 @@
       <c r="Y33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="Z33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -3160,6 +3297,9 @@
         <v>4</v>
       </c>
       <c r="Y34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2398182-3E75-40AF-A18C-B5A9A76A47F5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D67949-6508-4BEE-8BD3-26CFE0650804}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -485,7 +485,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -509,7 +509,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -739,10 +738,10 @@
     <col min="9" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="26" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -821,8 +820,11 @@
       <c r="Z3" s="5">
         <v>45044</v>
       </c>
+      <c r="AA3" s="5">
+        <v>45045</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -901,8 +903,11 @@
       <c r="Z4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -981,8 +986,11 @@
       <c r="Z5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1061,8 +1069,11 @@
       <c r="Z6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1141,8 +1152,11 @@
       <c r="Z7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1221,8 +1235,11 @@
       <c r="Z8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1301,8 +1318,11 @@
       <c r="Z9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1381,8 +1401,11 @@
       <c r="Z10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1461,8 +1484,11 @@
       <c r="Z11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1541,8 +1567,11 @@
       <c r="Z12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1621,8 +1650,11 @@
       <c r="Z13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -1701,8 +1733,11 @@
       <c r="Z14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -1781,8 +1816,11 @@
       <c r="Z15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -1859,6 +1897,9 @@
         <v>4</v>
       </c>
       <c r="Z16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA16" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1941,6 +1982,9 @@
       <c r="Z17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
@@ -2021,7 +2065,9 @@
       <c r="Z18" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AA18" s="11"/>
+      <c r="AA18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
@@ -2102,6 +2148,9 @@
       <c r="Z19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="20" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
@@ -2182,6 +2231,9 @@
       <c r="Z20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
@@ -2262,6 +2314,9 @@
       <c r="Z21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
@@ -2342,6 +2397,9 @@
       <c r="Z22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
@@ -2422,6 +2480,9 @@
       <c r="Z23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="24" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
@@ -2502,6 +2563,9 @@
       <c r="Z24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
@@ -2582,6 +2646,9 @@
       <c r="Z25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="26" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
@@ -2662,6 +2729,9 @@
       <c r="Z26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="27" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
@@ -2742,6 +2812,9 @@
       <c r="Z27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
@@ -2822,6 +2895,9 @@
       <c r="Z28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
@@ -2902,6 +2978,9 @@
       <c r="Z29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="30" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
@@ -2982,6 +3061,9 @@
       <c r="Z30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
@@ -3062,6 +3144,9 @@
       <c r="Z31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
@@ -3142,8 +3227,11 @@
       <c r="Z32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -3222,8 +3310,11 @@
       <c r="Z33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AA33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -3300,6 +3391,9 @@
         <v>4</v>
       </c>
       <c r="Z34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D67949-6508-4BEE-8BD3-26CFE0650804}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E7E6B2-66DF-4F23-8BAA-5BE88E2EB21F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,6 +50,20 @@
             <charset val="1"/>
           </rPr>
           <t>9:01</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AB10" authorId="0" shapeId="0" xr:uid="{3E374D75-3895-49F1-B346-BE43AE381426}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
         </r>
       </text>
     </comment>
@@ -109,6 +123,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AB18" authorId="0" shapeId="0" xr:uid="{FD2907B2-265D-479D-B926-DE6BFF559549}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:05</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="X20" authorId="0" shapeId="0" xr:uid="{DA902251-6155-45D0-BF90-7E5F5DFDE287}">
       <text>
         <r>
@@ -123,6 +151,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AB20" authorId="0" shapeId="0" xr:uid="{4EDCF199-6577-48DD-8316-4B1256E504EB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z22" authorId="0" shapeId="0" xr:uid="{DDD8C7AD-47C9-4E11-8FE8-07117ACB2789}">
       <text>
         <r>
@@ -134,6 +176,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:02</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AB22" authorId="0" shapeId="0" xr:uid="{E61CEF60-F6F8-453C-A315-5E55CD5CB4E8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:05</t>
         </r>
       </text>
     </comment>
@@ -184,7 +240,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -485,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -509,6 +565,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -724,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:AA34"/>
+  <dimension ref="A3:AC34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -739,9 +796,10 @@
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:27" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -823,8 +881,11 @@
       <c r="AA3" s="5">
         <v>45045</v>
       </c>
+      <c r="AB3" s="5">
+        <v>45048</v>
+      </c>
     </row>
-    <row r="4" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -906,8 +967,11 @@
       <c r="AA4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -989,8 +1053,11 @@
       <c r="AA5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1072,8 +1139,11 @@
       <c r="AA6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1155,8 +1225,11 @@
       <c r="AA7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1238,8 +1311,11 @@
       <c r="AA8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1321,8 +1397,11 @@
       <c r="AA9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1404,8 +1483,12 @@
       <c r="AA10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="11"/>
     </row>
-    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1487,8 +1570,11 @@
       <c r="AA11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1570,8 +1656,11 @@
       <c r="AA12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1653,8 +1742,11 @@
       <c r="AA13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -1736,8 +1828,11 @@
       <c r="AA14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -1819,8 +1914,11 @@
       <c r="AA15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -1902,8 +2000,11 @@
       <c r="AA16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -1985,8 +2086,11 @@
       <c r="AA17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -2068,8 +2172,11 @@
       <c r="AA18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -2151,8 +2258,11 @@
       <c r="AA19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -2234,8 +2344,11 @@
       <c r="AA20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -2317,8 +2430,11 @@
       <c r="AA21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -2400,8 +2516,11 @@
       <c r="AA22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -2483,8 +2602,11 @@
       <c r="AA23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -2566,8 +2688,11 @@
       <c r="AA24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -2649,8 +2774,11 @@
       <c r="AA25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -2732,8 +2860,11 @@
       <c r="AA26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -2815,8 +2946,11 @@
       <c r="AA27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -2898,8 +3032,11 @@
       <c r="AA28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -2981,8 +3118,11 @@
       <c r="AA29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -3064,8 +3204,11 @@
       <c r="AA30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -3147,8 +3290,11 @@
       <c r="AA31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -3230,8 +3376,11 @@
       <c r="AA32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -3313,8 +3462,11 @@
       <c r="AA33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AB33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -3394,6 +3546,9 @@
         <v>4</v>
       </c>
       <c r="AA34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E7E6B2-66DF-4F23-8BAA-5BE88E2EB21F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B11BCC-A926-415F-8A51-15605316E67D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,6 +67,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AC10" authorId="0" shapeId="0" xr:uid="{E1A43664-023D-4F9C-873D-65DD78E3FFAA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="N13" authorId="0" shapeId="0" xr:uid="{FDBC7F03-2036-496C-8DA4-E2730B6FDC9C}">
       <text>
         <r>
@@ -106,6 +120,21 @@
             <charset val="1"/>
           </rPr>
           <t>9:04</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC13" authorId="0" shapeId="0" xr:uid="{4D37337C-DB8C-4C60-AB0D-328AB244638A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>9:01
+Has come at 8:40. Kept the bag and went out.</t>
         </r>
       </text>
     </comment>
@@ -165,6 +194,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AC20" authorId="0" shapeId="0" xr:uid="{543E78A1-2E5B-40A9-A976-A844F9DC23F3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:05</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z22" authorId="0" shapeId="0" xr:uid="{DDD8C7AD-47C9-4E11-8FE8-07117ACB2789}">
       <text>
         <r>
@@ -221,6 +264,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AC30" authorId="0" shapeId="0" xr:uid="{5B87CF9A-0630-45DA-8168-365F756AFFD1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z32" authorId="0" shapeId="0" xr:uid="{59E0B9C2-F2EA-4082-81B3-59239B204C71}">
       <text>
         <r>
@@ -240,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -781,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:AC34"/>
+  <dimension ref="A3:AD34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -796,10 +853,10 @@
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:29" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -884,8 +941,11 @@
       <c r="AB3" s="5">
         <v>45048</v>
       </c>
+      <c r="AC3" s="5">
+        <v>45049</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -970,8 +1030,11 @@
       <c r="AB4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1056,8 +1119,11 @@
       <c r="AB5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1142,8 +1208,11 @@
       <c r="AB6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1228,8 +1297,11 @@
       <c r="AB7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1314,8 +1386,11 @@
       <c r="AB8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1400,8 +1475,11 @@
       <c r="AB9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1486,9 +1564,11 @@
       <c r="AB10" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AC10" s="11"/>
+      <c r="AC10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1573,8 +1653,11 @@
       <c r="AB11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1659,8 +1742,11 @@
       <c r="AB12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1745,8 +1831,12 @@
       <c r="AB13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD13" s="11"/>
     </row>
-    <row r="14" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -1831,8 +1921,11 @@
       <c r="AB14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -1917,8 +2010,11 @@
       <c r="AB15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2003,8 +2099,11 @@
       <c r="AB16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2089,8 +2188,11 @@
       <c r="AB17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -2175,8 +2277,11 @@
       <c r="AB18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -2261,8 +2366,11 @@
       <c r="AB19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -2347,8 +2455,11 @@
       <c r="AB20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -2433,8 +2544,11 @@
       <c r="AB21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -2519,8 +2633,11 @@
       <c r="AB22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -2605,8 +2722,11 @@
       <c r="AB23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -2691,8 +2811,11 @@
       <c r="AB24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -2777,8 +2900,11 @@
       <c r="AB25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -2863,8 +2989,11 @@
       <c r="AB26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -2949,8 +3078,11 @@
       <c r="AB27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -3035,8 +3167,11 @@
       <c r="AB28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -3121,8 +3256,11 @@
       <c r="AB29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -3207,8 +3345,11 @@
       <c r="AB30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -3293,8 +3434,11 @@
       <c r="AB31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -3379,8 +3523,11 @@
       <c r="AB32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -3465,8 +3612,11 @@
       <c r="AB33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AC33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -3549,6 +3699,9 @@
         <v>4</v>
       </c>
       <c r="AB34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B11BCC-A926-415F-8A51-15605316E67D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57BA943-E8D5-4A25-880A-D88EBE36D244}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,6 +50,20 @@
             <charset val="1"/>
           </rPr>
           <t>9:01</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AD7" authorId="0" shapeId="0" xr:uid="{7FF4E1FD-3DA5-438B-927C-D120A9AC654F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
         </r>
       </text>
     </comment>
@@ -250,6 +264,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AD25" authorId="0" shapeId="0" xr:uid="{53893E74-952F-49A7-92F1-2A943C569993}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R29" authorId="0" shapeId="0" xr:uid="{80A47C8C-A3F5-499A-B36F-2D635D4CE47A}">
       <text>
         <r>
@@ -297,7 +325,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -838,7 +866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:AD34"/>
+  <dimension ref="A3:AE34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -853,10 +881,10 @@
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:30" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -944,8 +972,11 @@
       <c r="AC3" s="5">
         <v>45049</v>
       </c>
+      <c r="AD3" s="5">
+        <v>45050</v>
+      </c>
     </row>
-    <row r="4" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1033,8 +1064,11 @@
       <c r="AC4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1122,8 +1156,11 @@
       <c r="AC5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1211,8 +1248,11 @@
       <c r="AC6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1300,8 +1340,12 @@
       <c r="AC7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE7" s="11"/>
     </row>
-    <row r="8" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1389,8 +1433,11 @@
       <c r="AC8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1478,8 +1525,11 @@
       <c r="AC9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1567,8 +1617,11 @@
       <c r="AC10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1656,8 +1709,11 @@
       <c r="AC11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1745,8 +1801,11 @@
       <c r="AC12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1834,9 +1893,11 @@
       <c r="AC13" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AD13" s="11"/>
+      <c r="AD13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -1924,8 +1985,11 @@
       <c r="AC14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2013,8 +2077,11 @@
       <c r="AC15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2102,8 +2169,11 @@
       <c r="AC16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2191,8 +2261,11 @@
       <c r="AC17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -2280,8 +2353,11 @@
       <c r="AC18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -2369,8 +2445,11 @@
       <c r="AC19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -2458,8 +2537,11 @@
       <c r="AC20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -2547,8 +2629,11 @@
       <c r="AC21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -2636,8 +2721,11 @@
       <c r="AC22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -2725,8 +2813,11 @@
       <c r="AC23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -2814,8 +2905,11 @@
       <c r="AC24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -2903,8 +2997,11 @@
       <c r="AC25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -2992,8 +3089,11 @@
       <c r="AC26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -3081,8 +3181,11 @@
       <c r="AC27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -3170,8 +3273,11 @@
       <c r="AC28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -3259,8 +3365,11 @@
       <c r="AC29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -3348,8 +3457,11 @@
       <c r="AC30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -3437,8 +3549,11 @@
       <c r="AC31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -3526,8 +3641,11 @@
       <c r="AC32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -3615,8 +3733,11 @@
       <c r="AC33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AD33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -3702,6 +3823,9 @@
         <v>4</v>
       </c>
       <c r="AC34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57BA943-E8D5-4A25-880A-D88EBE36D244}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8005D5-B98F-47D2-8921-7BD1C3BD20B1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -325,7 +325,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -523,7 +523,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -622,6 +622,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -650,7 +661,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -866,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:AE34"/>
+  <dimension ref="A3:AF34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -881,10 +894,10 @@
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="31" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:31" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -975,8 +988,11 @@
       <c r="AD3" s="5">
         <v>45050</v>
       </c>
+      <c r="AE3" s="5">
+        <v>45051</v>
+      </c>
     </row>
-    <row r="4" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1067,8 +1083,11 @@
       <c r="AD4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1159,8 +1178,11 @@
       <c r="AD5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1251,8 +1273,12 @@
       <c r="AD6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF6" s="11"/>
     </row>
-    <row r="7" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1343,9 +1369,11 @@
       <c r="AD7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AE7" s="11"/>
+      <c r="AE7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1436,8 +1464,11 @@
       <c r="AD8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1528,8 +1559,11 @@
       <c r="AD9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1620,8 +1654,11 @@
       <c r="AD10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1712,8 +1749,11 @@
       <c r="AD11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1804,8 +1844,11 @@
       <c r="AD12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1896,8 +1939,11 @@
       <c r="AD13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -1988,8 +2034,11 @@
       <c r="AD14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2080,8 +2129,11 @@
       <c r="AD15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2172,8 +2224,11 @@
       <c r="AD16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2264,8 +2319,11 @@
       <c r="AD17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -2356,8 +2414,11 @@
       <c r="AD18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -2448,8 +2509,11 @@
       <c r="AD19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -2540,8 +2604,11 @@
       <c r="AD20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -2632,8 +2699,11 @@
       <c r="AD21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -2724,8 +2794,11 @@
       <c r="AD22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -2816,8 +2889,11 @@
       <c r="AD23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -2908,8 +2984,11 @@
       <c r="AD24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -3000,8 +3079,11 @@
       <c r="AD25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -3092,8 +3174,11 @@
       <c r="AD26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -3184,8 +3269,11 @@
       <c r="AD27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -3276,8 +3364,11 @@
       <c r="AD28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -3368,8 +3459,11 @@
       <c r="AD29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -3460,8 +3554,11 @@
       <c r="AD30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -3552,8 +3649,11 @@
       <c r="AD31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -3644,8 +3744,11 @@
       <c r="AD32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -3736,8 +3839,11 @@
       <c r="AD33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AE33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -3826,6 +3932,9 @@
         <v>4</v>
       </c>
       <c r="AD34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8005D5-B98F-47D2-8921-7BD1C3BD20B1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FC992D-7CC5-46F9-A6B1-0EA21A9FEDDD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -325,7 +325,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -523,7 +523,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -622,22 +622,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -660,9 +649,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -894,7 +880,7 @@
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="31" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="32" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:32" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -991,6 +977,9 @@
       <c r="AE3" s="5">
         <v>45051</v>
       </c>
+      <c r="AF3" s="5">
+        <v>45052</v>
+      </c>
     </row>
     <row r="4" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
@@ -1086,6 +1075,9 @@
       <c r="AE4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
@@ -1181,6 +1173,9 @@
       <c r="AE5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
@@ -1276,7 +1271,9 @@
       <c r="AE6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AF6" s="11"/>
+      <c r="AF6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
@@ -1370,6 +1367,9 @@
         <v>4</v>
       </c>
       <c r="AE7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF7" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1467,6 +1467,9 @@
       <c r="AE8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
@@ -1562,6 +1565,9 @@
       <c r="AE9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
@@ -1657,6 +1663,9 @@
       <c r="AE10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
@@ -1752,6 +1761,9 @@
       <c r="AE11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
@@ -1847,6 +1859,9 @@
       <c r="AE12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
@@ -1942,6 +1957,9 @@
       <c r="AE13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
@@ -2037,6 +2055,9 @@
       <c r="AE14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
@@ -2132,6 +2153,9 @@
       <c r="AE15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
@@ -2227,8 +2251,11 @@
       <c r="AE16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2322,8 +2349,11 @@
       <c r="AE17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -2417,8 +2447,11 @@
       <c r="AE18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -2512,8 +2545,11 @@
       <c r="AE19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -2607,8 +2643,11 @@
       <c r="AE20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -2702,8 +2741,11 @@
       <c r="AE21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -2797,8 +2839,11 @@
       <c r="AE22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -2892,8 +2937,11 @@
       <c r="AE23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -2987,8 +3035,11 @@
       <c r="AE24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -3082,8 +3133,11 @@
       <c r="AE25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -3177,8 +3231,11 @@
       <c r="AE26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -3272,8 +3329,11 @@
       <c r="AE27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -3367,8 +3427,11 @@
       <c r="AE28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -3462,8 +3525,11 @@
       <c r="AE29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -3557,8 +3623,11 @@
       <c r="AE30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -3652,8 +3721,11 @@
       <c r="AE31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -3747,8 +3819,11 @@
       <c r="AE32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -3842,8 +3917,11 @@
       <c r="AE33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AF33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -3935,6 +4013,9 @@
         <v>4</v>
       </c>
       <c r="AE34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FC992D-7CC5-46F9-A6B1-0EA21A9FEDDD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F72EF6-5F20-4C81-8162-6BF0D38790C5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -278,6 +278,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AG25" authorId="0" shapeId="0" xr:uid="{C86D4A58-746B-4B41-AB52-C772E4F546A0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:03</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R29" authorId="0" shapeId="0" xr:uid="{80A47C8C-A3F5-499A-B36F-2D635D4CE47A}">
       <text>
         <r>
@@ -325,7 +339,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -865,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:AF34"/>
+  <dimension ref="A3:AG34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -880,10 +894,10 @@
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="32" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="33" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:32" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -980,8 +994,11 @@
       <c r="AF3" s="5">
         <v>45052</v>
       </c>
+      <c r="AG3" s="5">
+        <v>45054</v>
+      </c>
     </row>
-    <row r="4" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1078,8 +1095,11 @@
       <c r="AF4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1176,8 +1196,11 @@
       <c r="AF5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1274,8 +1297,11 @@
       <c r="AF6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1372,8 +1398,11 @@
       <c r="AF7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1470,8 +1499,11 @@
       <c r="AF8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1568,8 +1600,11 @@
       <c r="AF9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1666,8 +1701,11 @@
       <c r="AF10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1764,8 +1802,11 @@
       <c r="AF11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1862,8 +1903,11 @@
       <c r="AF12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1960,8 +2004,11 @@
       <c r="AF13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2058,8 +2105,11 @@
       <c r="AF14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2156,8 +2206,11 @@
       <c r="AF15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2254,8 +2307,11 @@
       <c r="AF16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2352,8 +2408,11 @@
       <c r="AF17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -2450,8 +2509,11 @@
       <c r="AF18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -2548,8 +2610,11 @@
       <c r="AF19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -2646,8 +2711,11 @@
       <c r="AF20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -2744,8 +2812,11 @@
       <c r="AF21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -2842,8 +2913,11 @@
       <c r="AF22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -2940,8 +3014,11 @@
       <c r="AF23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -3038,8 +3115,11 @@
       <c r="AF24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -3136,8 +3216,11 @@
       <c r="AF25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -3234,8 +3317,11 @@
       <c r="AF26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -3332,8 +3418,11 @@
       <c r="AF27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -3430,8 +3519,11 @@
       <c r="AF28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -3528,8 +3620,11 @@
       <c r="AF29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -3626,8 +3721,11 @@
       <c r="AF30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -3724,8 +3822,11 @@
       <c r="AF31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -3822,8 +3923,11 @@
       <c r="AF32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -3920,8 +4024,11 @@
       <c r="AF33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AG33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -4016,6 +4123,9 @@
         <v>4</v>
       </c>
       <c r="AF34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F72EF6-5F20-4C81-8162-6BF0D38790C5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B665DAF8-17FC-45BF-9128-F64720DC2527}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,6 +292,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AH25" authorId="0" shapeId="0" xr:uid="{3556CA4B-6F8A-4952-9B7E-B0DB7E65E4EE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R29" authorId="0" shapeId="0" xr:uid="{80A47C8C-A3F5-499A-B36F-2D635D4CE47A}">
       <text>
         <r>
@@ -339,7 +353,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -537,7 +551,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -636,11 +650,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -663,6 +688,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -879,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:AG34"/>
+  <dimension ref="A3:AI34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -894,10 +922,10 @@
     <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="33" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:33" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -997,8 +1025,11 @@
       <c r="AG3" s="5">
         <v>45054</v>
       </c>
+      <c r="AH3" s="5">
+        <v>45055</v>
+      </c>
     </row>
-    <row r="4" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1098,8 +1129,11 @@
       <c r="AG4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1199,8 +1233,11 @@
       <c r="AG5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1300,8 +1337,11 @@
       <c r="AG6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH6" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="7" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1401,8 +1441,11 @@
       <c r="AG7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1502,8 +1545,11 @@
       <c r="AG8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1603,8 +1649,11 @@
       <c r="AG9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1704,8 +1753,11 @@
       <c r="AG10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1805,8 +1857,11 @@
       <c r="AG11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1906,8 +1961,11 @@
       <c r="AG12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2007,8 +2065,11 @@
       <c r="AG13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2108,8 +2169,11 @@
       <c r="AG14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2209,8 +2273,11 @@
       <c r="AG15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2310,8 +2377,11 @@
       <c r="AG16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2411,8 +2481,11 @@
       <c r="AG17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -2512,8 +2585,11 @@
       <c r="AG18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -2613,8 +2689,11 @@
       <c r="AG19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -2714,8 +2793,11 @@
       <c r="AG20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -2815,8 +2897,11 @@
       <c r="AG21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -2916,8 +3001,11 @@
       <c r="AG22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -3017,8 +3105,11 @@
       <c r="AG23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -3118,8 +3209,11 @@
       <c r="AG24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -3219,8 +3313,11 @@
       <c r="AG25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -3320,8 +3417,11 @@
       <c r="AG26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -3421,8 +3521,11 @@
       <c r="AG27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -3522,8 +3625,11 @@
       <c r="AG28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -3623,8 +3729,11 @@
       <c r="AG29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -3724,8 +3833,12 @@
       <c r="AG30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI30" s="11"/>
     </row>
-    <row r="31" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -3825,8 +3938,11 @@
       <c r="AG31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -3926,8 +4042,11 @@
       <c r="AG32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -4027,8 +4146,11 @@
       <c r="AG33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AH33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -4126,6 +4248,9 @@
         <v>4</v>
       </c>
       <c r="AG34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B665DAF8-17FC-45BF-9128-F64720DC2527}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214A0DE2-2B12-412C-B3BC-39020223CB54}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -353,7 +353,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -551,7 +551,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -650,22 +650,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -688,9 +677,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -923,9 +909,10 @@
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:34" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1028,8 +1015,11 @@
       <c r="AH3" s="5">
         <v>45055</v>
       </c>
+      <c r="AI3" s="5">
+        <v>45056</v>
+      </c>
     </row>
-    <row r="4" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1132,8 +1122,11 @@
       <c r="AH4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1236,8 +1229,11 @@
       <c r="AH5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1340,8 +1336,11 @@
       <c r="AH6" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="AI6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1444,8 +1443,11 @@
       <c r="AH7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1548,8 +1550,11 @@
       <c r="AH8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1652,8 +1657,11 @@
       <c r="AH9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1756,8 +1764,11 @@
       <c r="AH10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1860,8 +1871,11 @@
       <c r="AH11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1964,8 +1978,11 @@
       <c r="AH12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2068,8 +2085,11 @@
       <c r="AH13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2172,8 +2192,11 @@
       <c r="AH14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2276,8 +2299,11 @@
       <c r="AH15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2378,6 +2404,9 @@
         <v>4</v>
       </c>
       <c r="AH16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI16" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2484,6 +2513,9 @@
       <c r="AH17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
@@ -2588,6 +2620,9 @@
       <c r="AH18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="19" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
@@ -2692,6 +2727,9 @@
       <c r="AH19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="20" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
@@ -2796,6 +2834,9 @@
       <c r="AH20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
@@ -2900,6 +2941,9 @@
       <c r="AH21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
@@ -3004,6 +3048,9 @@
       <c r="AH22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
@@ -3108,6 +3155,9 @@
       <c r="AH23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="24" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
@@ -3212,6 +3262,9 @@
       <c r="AH24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="25" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
@@ -3316,6 +3369,9 @@
       <c r="AH25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="26" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
@@ -3420,6 +3476,9 @@
       <c r="AH26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="27" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
@@ -3524,6 +3583,9 @@
       <c r="AH27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
@@ -3628,6 +3690,9 @@
       <c r="AH28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="29" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
@@ -3732,6 +3797,9 @@
       <c r="AH29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="30" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
@@ -3836,7 +3904,9 @@
       <c r="AH30" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AI30" s="11"/>
+      <c r="AI30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
@@ -3941,6 +4011,9 @@
       <c r="AH31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
@@ -4045,8 +4118,11 @@
       <c r="AH32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -4149,8 +4225,11 @@
       <c r="AH33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AI33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -4251,6 +4330,9 @@
         <v>4</v>
       </c>
       <c r="AH34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214A0DE2-2B12-412C-B3BC-39020223CB54}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2034D64A-141B-4643-8C97-2280E11E3DFE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -353,7 +353,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -893,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:AI34"/>
+  <dimension ref="A3:AJ34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -909,10 +909,10 @@
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:35" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1018,8 +1018,11 @@
       <c r="AI3" s="5">
         <v>45056</v>
       </c>
+      <c r="AJ3" s="5">
+        <v>45057</v>
+      </c>
     </row>
-    <row r="4" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1125,8 +1128,11 @@
       <c r="AI4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1232,8 +1238,11 @@
       <c r="AI5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1339,8 +1348,11 @@
       <c r="AI6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1446,8 +1458,11 @@
       <c r="AI7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1553,8 +1568,11 @@
       <c r="AI8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1660,8 +1678,11 @@
       <c r="AI9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1767,8 +1788,11 @@
       <c r="AI10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1874,8 +1898,11 @@
       <c r="AI11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1981,8 +2008,11 @@
       <c r="AI12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2088,8 +2118,11 @@
       <c r="AI13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2195,8 +2228,11 @@
       <c r="AI14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2302,8 +2338,11 @@
       <c r="AI15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2409,8 +2448,11 @@
       <c r="AI16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2516,8 +2558,11 @@
       <c r="AI17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -2623,8 +2668,11 @@
       <c r="AI18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -2730,8 +2778,11 @@
       <c r="AI19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -2837,8 +2888,11 @@
       <c r="AI20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -2944,8 +2998,11 @@
       <c r="AI21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -3051,8 +3108,11 @@
       <c r="AI22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -3158,8 +3218,11 @@
       <c r="AI23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -3265,8 +3328,11 @@
       <c r="AI24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -3372,8 +3438,11 @@
       <c r="AI25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -3479,8 +3548,11 @@
       <c r="AI26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -3586,8 +3658,11 @@
       <c r="AI27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -3693,8 +3768,11 @@
       <c r="AI28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -3800,8 +3878,11 @@
       <c r="AI29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -3907,8 +3988,11 @@
       <c r="AI30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -4014,8 +4098,11 @@
       <c r="AI31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -4121,8 +4208,11 @@
       <c r="AI32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -4228,8 +4318,11 @@
       <c r="AI33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AJ33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -4333,6 +4426,9 @@
         <v>4</v>
       </c>
       <c r="AI34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2034D64A-141B-4643-8C97-2280E11E3DFE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E17654A-CEFE-4D7D-81D8-34E1C6E22813}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -222,6 +222,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AK20" authorId="0" shapeId="0" xr:uid="{D2CF3B78-535C-46A5-AA6C-2C56923D2A2D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z22" authorId="0" shapeId="0" xr:uid="{DDD8C7AD-47C9-4E11-8FE8-07117ACB2789}">
       <text>
         <r>
@@ -306,6 +320,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AL25" authorId="0" shapeId="0" xr:uid="{CFA12068-5686-45CD-BE3A-F8A4A196BBDD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:06</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R29" authorId="0" shapeId="0" xr:uid="{80A47C8C-A3F5-499A-B36F-2D635D4CE47A}">
       <text>
         <r>
@@ -353,7 +381,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -654,7 +682,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -677,6 +705,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -893,7 +924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:AJ34"/>
+  <dimension ref="A3:AL34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -909,10 +940,10 @@
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="35" max="38" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1021,8 +1052,14 @@
       <c r="AJ3" s="5">
         <v>45057</v>
       </c>
+      <c r="AK3" s="5">
+        <v>45058</v>
+      </c>
+      <c r="AL3" s="5">
+        <v>45061</v>
+      </c>
     </row>
-    <row r="4" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1131,8 +1168,14 @@
       <c r="AJ4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1241,8 +1284,14 @@
       <c r="AJ5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1351,8 +1400,14 @@
       <c r="AJ6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1461,8 +1516,14 @@
       <c r="AJ7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1571,8 +1632,14 @@
       <c r="AJ8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1681,8 +1748,14 @@
       <c r="AJ9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1791,8 +1864,14 @@
       <c r="AJ10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1901,8 +1980,14 @@
       <c r="AJ11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2011,8 +2096,14 @@
       <c r="AJ12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2121,8 +2212,14 @@
       <c r="AJ13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2231,8 +2328,14 @@
       <c r="AJ14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2341,8 +2444,14 @@
       <c r="AJ15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2451,8 +2560,14 @@
       <c r="AJ16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2561,8 +2676,14 @@
       <c r="AJ17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -2671,8 +2792,14 @@
       <c r="AJ18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -2781,8 +2908,14 @@
       <c r="AJ19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -2891,8 +3024,14 @@
       <c r="AJ20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK20" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -3001,8 +3140,14 @@
       <c r="AJ21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -3111,8 +3256,14 @@
       <c r="AJ22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -3221,8 +3372,14 @@
       <c r="AJ23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -3331,8 +3488,14 @@
       <c r="AJ24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -3441,8 +3604,14 @@
       <c r="AJ25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -3551,8 +3720,14 @@
       <c r="AJ26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -3661,8 +3836,14 @@
       <c r="AJ27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -3771,8 +3952,14 @@
       <c r="AJ28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK28" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -3881,8 +4068,14 @@
       <c r="AJ29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -3991,8 +4184,14 @@
       <c r="AJ30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -4101,8 +4300,14 @@
       <c r="AJ31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -4211,8 +4416,14 @@
       <c r="AJ32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -4321,8 +4532,14 @@
       <c r="AJ33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AK33" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -4429,6 +4646,12 @@
         <v>4</v>
       </c>
       <c r="AJ34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E17654A-CEFE-4D7D-81D8-34E1C6E22813}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3B8940-8E86-4BD0-B10A-8CBFCF7BD724}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -236,6 +236,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AM20" authorId="0" shapeId="0" xr:uid="{7C5720D1-D054-44D4-8D4C-26FCBAEBF094}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z22" authorId="0" shapeId="0" xr:uid="{DDD8C7AD-47C9-4E11-8FE8-07117ACB2789}">
       <text>
         <r>
@@ -381,7 +395,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -924,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:AL34"/>
+  <dimension ref="A3:AM34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -940,10 +954,10 @@
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="35" max="38" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="35" max="39" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:38" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1058,8 +1072,11 @@
       <c r="AL3" s="5">
         <v>45061</v>
       </c>
+      <c r="AM3" s="5">
+        <v>45062</v>
+      </c>
     </row>
-    <row r="4" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1174,8 +1191,11 @@
       <c r="AL4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1290,8 +1310,11 @@
       <c r="AL5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1406,8 +1429,11 @@
       <c r="AL6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1522,8 +1548,11 @@
       <c r="AL7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1638,8 +1667,11 @@
       <c r="AL8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1754,8 +1786,11 @@
       <c r="AL9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1870,8 +1905,11 @@
       <c r="AL10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1986,8 +2024,11 @@
       <c r="AL11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2102,8 +2143,11 @@
       <c r="AL12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2218,8 +2262,11 @@
       <c r="AL13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2334,8 +2381,11 @@
       <c r="AL14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2450,8 +2500,11 @@
       <c r="AL15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2566,8 +2619,11 @@
       <c r="AL16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2682,8 +2738,11 @@
       <c r="AL17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -2798,8 +2857,11 @@
       <c r="AL18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -2914,8 +2976,11 @@
       <c r="AL19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -3030,8 +3095,11 @@
       <c r="AL20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -3146,8 +3214,11 @@
       <c r="AL21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -3262,8 +3333,11 @@
       <c r="AL22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -3378,8 +3452,11 @@
       <c r="AL23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -3494,8 +3571,11 @@
       <c r="AL24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -3610,8 +3690,11 @@
       <c r="AL25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -3726,8 +3809,11 @@
       <c r="AL26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -3842,8 +3928,11 @@
       <c r="AL27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -3958,8 +4047,11 @@
       <c r="AL28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -4074,8 +4166,11 @@
       <c r="AL29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -4190,8 +4285,11 @@
       <c r="AL30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -4306,8 +4404,11 @@
       <c r="AL31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -4422,8 +4523,11 @@
       <c r="AL32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -4538,8 +4642,11 @@
       <c r="AL33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AM33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -4652,6 +4759,9 @@
         <v>4</v>
       </c>
       <c r="AL34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3B8940-8E86-4BD0-B10A-8CBFCF7BD724}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E7E558-10FF-4C6E-B3CC-FA8D6C03CD60}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -236,7 +236,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AM20" authorId="0" shapeId="0" xr:uid="{7C5720D1-D054-44D4-8D4C-26FCBAEBF094}">
+    <comment ref="AN20" authorId="0" shapeId="0" xr:uid="{7C5720D1-D054-44D4-8D4C-26FCBAEBF094}">
       <text>
         <r>
           <rPr>
@@ -334,7 +334,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AL25" authorId="0" shapeId="0" xr:uid="{CFA12068-5686-45CD-BE3A-F8A4A196BBDD}">
+    <comment ref="AM25" authorId="0" shapeId="0" xr:uid="{CFA12068-5686-45CD-BE3A-F8A4A196BBDD}">
       <text>
         <r>
           <rPr>
@@ -395,7 +395,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -938,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:AM34"/>
+  <dimension ref="A1:AO34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -954,10 +954,18 @@
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="35" max="39" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.77734375" customWidth="1"/>
+    <col min="39" max="41" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:39" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AO1">
+        <f>COUNTA(AO4:AO34)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1070,13 +1078,19 @@
         <v>45058</v>
       </c>
       <c r="AL3" s="5">
+        <v>45059</v>
+      </c>
+      <c r="AM3" s="5">
         <v>45061</v>
       </c>
-      <c r="AM3" s="5">
+      <c r="AN3" s="5">
         <v>45062</v>
       </c>
+      <c r="AO3" s="5">
+        <v>45063</v>
+      </c>
     </row>
-    <row r="4" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1194,8 +1208,14 @@
       <c r="AM4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1313,8 +1333,14 @@
       <c r="AM5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1432,8 +1458,14 @@
       <c r="AM6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1551,8 +1583,14 @@
       <c r="AM7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1670,8 +1708,14 @@
       <c r="AM8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1789,8 +1833,14 @@
       <c r="AM9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1908,8 +1958,14 @@
       <c r="AM10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -2027,8 +2083,14 @@
       <c r="AM11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2146,8 +2208,14 @@
       <c r="AM12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2265,8 +2333,14 @@
       <c r="AM13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2384,8 +2458,14 @@
       <c r="AM14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2503,8 +2583,14 @@
       <c r="AM15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2622,8 +2708,14 @@
       <c r="AM16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2741,8 +2833,14 @@
       <c r="AM17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -2860,8 +2958,14 @@
       <c r="AM18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -2979,8 +3083,14 @@
       <c r="AM19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -3098,8 +3208,14 @@
       <c r="AM20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -3217,8 +3333,14 @@
       <c r="AM21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -3336,8 +3458,14 @@
       <c r="AM22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -3455,8 +3583,14 @@
       <c r="AM23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -3574,8 +3708,14 @@
       <c r="AM24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -3693,8 +3833,14 @@
       <c r="AM25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -3812,8 +3958,14 @@
       <c r="AM26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -3931,8 +4083,14 @@
       <c r="AM27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -4050,8 +4208,14 @@
       <c r="AM28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN28" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -4169,8 +4333,14 @@
       <c r="AM29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -4288,8 +4458,14 @@
       <c r="AM30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -4407,8 +4583,14 @@
       <c r="AM31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -4526,8 +4708,14 @@
       <c r="AM32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -4645,8 +4833,14 @@
       <c r="AM33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AN33" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -4762,6 +4956,12 @@
         <v>4</v>
       </c>
       <c r="AM34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E7E558-10FF-4C6E-B3CC-FA8D6C03CD60}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF4AD1D-AF8D-4644-851A-284C2E5F61B0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -938,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:AO34"/>
+  <dimension ref="A3:AO34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -959,12 +959,6 @@
     <col min="39" max="41" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="AO1">
-        <f>COUNTA(AO4:AO34)</f>
-        <v>31</v>
-      </c>
-    </row>
     <row r="3" spans="1:41" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF4AD1D-AF8D-4644-851A-284C2E5F61B0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5403618-5E46-444C-8926-B826A0EC3597}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -395,7 +395,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -938,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:AO34"/>
+  <dimension ref="A3:AP34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -956,10 +956,10 @@
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
-    <col min="39" max="41" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="42" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:41" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:42" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1083,8 +1083,11 @@
       <c r="AO3" s="5">
         <v>45063</v>
       </c>
+      <c r="AP3" s="5">
+        <v>45064</v>
+      </c>
     </row>
-    <row r="4" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1208,8 +1211,11 @@
       <c r="AO4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1333,8 +1339,11 @@
       <c r="AO5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1458,8 +1467,11 @@
       <c r="AO6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1583,8 +1595,11 @@
       <c r="AO7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1708,8 +1723,11 @@
       <c r="AO8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1833,8 +1851,11 @@
       <c r="AO9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1958,8 +1979,11 @@
       <c r="AO10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -2083,8 +2107,11 @@
       <c r="AO11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2208,8 +2235,11 @@
       <c r="AO12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2333,8 +2363,11 @@
       <c r="AO13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2458,8 +2491,11 @@
       <c r="AO14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2583,8 +2619,11 @@
       <c r="AO15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2708,8 +2747,11 @@
       <c r="AO16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2833,8 +2875,11 @@
       <c r="AO17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -2958,8 +3003,11 @@
       <c r="AO18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -3083,8 +3131,11 @@
       <c r="AO19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -3208,8 +3259,11 @@
       <c r="AO20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -3333,8 +3387,11 @@
       <c r="AO21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -3458,8 +3515,11 @@
       <c r="AO22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -3583,8 +3643,11 @@
       <c r="AO23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -3708,8 +3771,11 @@
       <c r="AO24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -3833,8 +3899,11 @@
       <c r="AO25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -3958,8 +4027,11 @@
       <c r="AO26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -4083,8 +4155,11 @@
       <c r="AO27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -4208,8 +4283,11 @@
       <c r="AO28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -4333,8 +4411,11 @@
       <c r="AO29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -4458,8 +4539,11 @@
       <c r="AO30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -4583,8 +4667,11 @@
       <c r="AO31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -4708,8 +4795,11 @@
       <c r="AO32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -4833,8 +4923,11 @@
       <c r="AO33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AP33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -4956,6 +5049,9 @@
         <v>4</v>
       </c>
       <c r="AO34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5403618-5E46-444C-8926-B826A0EC3597}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3365415A-D65A-4770-8B3F-7F78F474F63C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,6 +92,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:02</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AR12" authorId="0" shapeId="0" xr:uid="{545F614C-5FF6-474D-A0CA-692648A0BE68}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04</t>
         </r>
       </text>
     </comment>
@@ -250,6 +264,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AQ20" authorId="0" shapeId="0" xr:uid="{F045718E-AD1B-4127-B027-D4BF591A83AC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z22" authorId="0" shapeId="0" xr:uid="{DDD8C7AD-47C9-4E11-8FE8-07117ACB2789}">
       <text>
         <r>
@@ -275,6 +303,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:05</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AR24" authorId="0" shapeId="0" xr:uid="{93A2F35A-C324-4F57-AAF5-D02DB505B765}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04</t>
         </r>
       </text>
     </comment>
@@ -348,6 +390,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AQ25" authorId="0" shapeId="0" xr:uid="{C1A1DA7D-6B21-4348-87FA-5B530AC69622}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R29" authorId="0" shapeId="0" xr:uid="{80A47C8C-A3F5-499A-B36F-2D635D4CE47A}">
       <text>
         <r>
@@ -395,7 +451,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -727,7 +783,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="5"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -938,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:AP34"/>
+  <dimension ref="A1:AR34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -956,10 +1020,20 @@
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
-    <col min="39" max="42" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="44" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:42" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AQ1">
+        <f>COUNTA(AQ4:AQ34)</f>
+        <v>31</v>
+      </c>
+      <c r="AR1">
+        <f>COUNTA(AR4:AR34)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:44" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1086,8 +1160,14 @@
       <c r="AP3" s="5">
         <v>45064</v>
       </c>
+      <c r="AQ3" s="5">
+        <v>45065</v>
+      </c>
+      <c r="AR3" s="5">
+        <v>45066</v>
+      </c>
     </row>
-    <row r="4" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1214,8 +1294,14 @@
       <c r="AP4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1342,8 +1428,14 @@
       <c r="AP5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1470,8 +1562,14 @@
       <c r="AP6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1598,8 +1696,14 @@
       <c r="AP7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1726,8 +1830,14 @@
       <c r="AP8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1854,8 +1964,14 @@
       <c r="AP9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1982,8 +2098,14 @@
       <c r="AP10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -2110,8 +2232,14 @@
       <c r="AP11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2238,8 +2366,14 @@
       <c r="AP12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2366,8 +2500,14 @@
       <c r="AP13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2494,8 +2634,14 @@
       <c r="AP14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2622,8 +2768,14 @@
       <c r="AP15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2750,8 +2902,14 @@
       <c r="AP16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2878,8 +3036,14 @@
       <c r="AP17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -3006,8 +3170,14 @@
       <c r="AP18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -3134,8 +3304,14 @@
       <c r="AP19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -3262,8 +3438,14 @@
       <c r="AP20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -3390,8 +3572,14 @@
       <c r="AP21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -3518,8 +3706,14 @@
       <c r="AP22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -3646,8 +3840,14 @@
       <c r="AP23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR23" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="24" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -3774,8 +3974,14 @@
       <c r="AP24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -3902,8 +4108,14 @@
       <c r="AP25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -4030,8 +4242,14 @@
       <c r="AP26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -4158,8 +4376,14 @@
       <c r="AP27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -4286,8 +4510,14 @@
       <c r="AP28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ28" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AR28" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="29" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -4414,8 +4644,14 @@
       <c r="AP29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -4542,8 +4778,14 @@
       <c r="AP30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -4670,8 +4912,14 @@
       <c r="AP31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -4798,8 +5046,14 @@
       <c r="AP32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -4926,8 +5180,14 @@
       <c r="AP33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AQ33" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -5052,6 +5312,12 @@
         <v>4</v>
       </c>
       <c r="AP34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3365415A-D65A-4770-8B3F-7F78F474F63C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1053ED16-FC36-42E8-AA4F-0CFBA7F0A2DB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -404,6 +404,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="AS25" authorId="0" shapeId="0" xr:uid="{00F9A794-D4DE-4F24-BA1C-A0B76011FB08}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:03</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AS27" authorId="0" shapeId="0" xr:uid="{E3CE2C02-3FD9-4256-B1DE-A8BDC78C9795}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R29" authorId="0" shapeId="0" xr:uid="{80A47C8C-A3F5-499A-B36F-2D635D4CE47A}">
       <text>
         <r>
@@ -451,7 +479,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -783,15 +811,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="5"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1002,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:AR34"/>
+  <dimension ref="A1:AS34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1020,10 +1040,10 @@
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
-    <col min="39" max="44" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="45" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="AQ1">
         <f>COUNTA(AQ4:AQ34)</f>
         <v>31</v>
@@ -1032,8 +1052,12 @@
         <f>COUNTA(AR4:AR34)</f>
         <v>31</v>
       </c>
+      <c r="AS1">
+        <f>COUNTA(AS4:AS34)</f>
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" spans="1:44" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:45" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1166,8 +1190,11 @@
       <c r="AR3" s="5">
         <v>45066</v>
       </c>
+      <c r="AS3" s="5">
+        <v>45068</v>
+      </c>
     </row>
-    <row r="4" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1300,8 +1327,11 @@
       <c r="AR4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1434,8 +1464,11 @@
       <c r="AR5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1568,8 +1601,11 @@
       <c r="AR6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1702,8 +1738,11 @@
       <c r="AR7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1836,8 +1875,11 @@
       <c r="AR8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1970,8 +2012,11 @@
       <c r="AR9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2104,8 +2149,11 @@
       <c r="AR10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -2238,8 +2286,11 @@
       <c r="AR11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2372,8 +2423,11 @@
       <c r="AR12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2506,8 +2560,11 @@
       <c r="AR13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2640,8 +2697,11 @@
       <c r="AR14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2774,8 +2834,11 @@
       <c r="AR15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2908,8 +2971,11 @@
       <c r="AR16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -3042,8 +3108,11 @@
       <c r="AR17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -3176,8 +3245,11 @@
       <c r="AR18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -3310,8 +3382,11 @@
       <c r="AR19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -3444,8 +3519,11 @@
       <c r="AR20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -3578,8 +3656,11 @@
       <c r="AR21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -3712,8 +3793,11 @@
       <c r="AR22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -3846,8 +3930,11 @@
       <c r="AR23" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="AS23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -3980,8 +4067,11 @@
       <c r="AR24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -4114,8 +4204,11 @@
       <c r="AR25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -4248,8 +4341,11 @@
       <c r="AR26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -4382,8 +4478,11 @@
       <c r="AR27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -4516,8 +4615,11 @@
       <c r="AR28" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="AS28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -4650,8 +4752,11 @@
       <c r="AR29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -4784,8 +4889,11 @@
       <c r="AR30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -4918,8 +5026,11 @@
       <c r="AR31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -5052,8 +5163,11 @@
       <c r="AR32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -5186,8 +5300,11 @@
       <c r="AR33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AS33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -5318,6 +5435,9 @@
         <v>4</v>
       </c>
       <c r="AR34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1053ED16-FC36-42E8-AA4F-0CFBA7F0A2DB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BCCD88-BE22-44FF-9880-9D83B5870122}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,6 +67,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AT7" authorId="0" shapeId="0" xr:uid="{19EF2AFB-F2F9-4411-A8CE-5174CDE8A3C3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AB10" authorId="0" shapeId="0" xr:uid="{3E374D75-3895-49F1-B346-BE43AE381426}">
       <text>
         <r>
@@ -92,6 +106,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:02</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AT10" authorId="0" shapeId="0" xr:uid="{95981924-40FA-4F18-93B1-8A72446587D3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
         </r>
       </text>
     </comment>
@@ -166,6 +194,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AT14" authorId="0" shapeId="0" xr:uid="{DF014D67-CF6A-43AC-954D-E6FB7EDDB7BE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:06</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z18" authorId="0" shapeId="0" xr:uid="{08D2A270-552A-494A-8EB7-D7239F622756}">
       <text>
         <r>
@@ -191,6 +233,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:05</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AT18" authorId="0" shapeId="0" xr:uid="{6DC118D3-7F38-443C-9748-3628CA01B1DE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:06</t>
         </r>
       </text>
     </comment>
@@ -306,6 +362,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AT22" authorId="0" shapeId="0" xr:uid="{66E36105-2D1E-4361-8EBA-BC56D9E7F7C3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:06</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AR24" authorId="0" shapeId="0" xr:uid="{93A2F35A-C324-4F57-AAF5-D02DB505B765}">
       <text>
         <r>
@@ -418,6 +488,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AT25" authorId="0" shapeId="0" xr:uid="{A5DC6BAD-544A-446A-8157-47E6097C991A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AS27" authorId="0" shapeId="0" xr:uid="{E3CE2C02-3FD9-4256-B1DE-A8BDC78C9795}">
       <text>
         <r>
@@ -474,12 +558,26 @@
         </r>
       </text>
     </comment>
+    <comment ref="AT32" authorId="0" shapeId="0" xr:uid="{BDF6BFD5-08CE-4A67-A540-3AFF86061929}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:06</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1022,7 +1120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:AS34"/>
+  <dimension ref="A1:AT34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1040,10 +1138,10 @@
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
-    <col min="39" max="45" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="46" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="AQ1">
         <f>COUNTA(AQ4:AQ34)</f>
         <v>31</v>
@@ -1056,8 +1154,12 @@
         <f>COUNTA(AS4:AS34)</f>
         <v>31</v>
       </c>
+      <c r="AT1">
+        <f>COUNTA(AT4:AT34)</f>
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" spans="1:45" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1193,8 +1295,11 @@
       <c r="AS3" s="5">
         <v>45068</v>
       </c>
+      <c r="AT3" s="5">
+        <v>45069</v>
+      </c>
     </row>
-    <row r="4" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1330,8 +1435,11 @@
       <c r="AS4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1467,8 +1575,11 @@
       <c r="AS5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1604,8 +1715,11 @@
       <c r="AS6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1741,8 +1855,11 @@
       <c r="AS7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1878,8 +1995,11 @@
       <c r="AS8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -2015,8 +2135,11 @@
       <c r="AS9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2152,8 +2275,11 @@
       <c r="AS10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -2289,8 +2415,11 @@
       <c r="AS11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2426,8 +2555,11 @@
       <c r="AS12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2563,8 +2695,11 @@
       <c r="AS13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2700,8 +2835,11 @@
       <c r="AS14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2837,8 +2975,11 @@
       <c r="AS15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2974,8 +3115,11 @@
       <c r="AS16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -3111,8 +3255,11 @@
       <c r="AS17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -3248,8 +3395,11 @@
       <c r="AS18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -3385,8 +3535,11 @@
       <c r="AS19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -3522,8 +3675,11 @@
       <c r="AS20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -3659,8 +3815,11 @@
       <c r="AS21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -3796,8 +3955,11 @@
       <c r="AS22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -3933,8 +4095,11 @@
       <c r="AS23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -4070,8 +4235,11 @@
       <c r="AS24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -4207,8 +4375,11 @@
       <c r="AS25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -4344,8 +4515,11 @@
       <c r="AS26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -4481,8 +4655,11 @@
       <c r="AS27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -4618,8 +4795,11 @@
       <c r="AS28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -4755,8 +4935,11 @@
       <c r="AS29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -4892,8 +5075,11 @@
       <c r="AS30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -5029,8 +5215,11 @@
       <c r="AS31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -5166,8 +5355,11 @@
       <c r="AS32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -5303,8 +5495,11 @@
       <c r="AS33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AT33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -5438,6 +5633,9 @@
         <v>4</v>
       </c>
       <c r="AS34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BCCD88-BE22-44FF-9880-9D83B5870122}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE355A77-7742-4826-9AE3-C22C25991B1B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -123,6 +123,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AU10" authorId="0" shapeId="0" xr:uid="{ABE98637-7F79-4752-8C73-0D2121A11108}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AR12" authorId="0" shapeId="0" xr:uid="{545F614C-5FF6-474D-A0CA-692648A0BE68}">
       <text>
         <r>
@@ -194,6 +208,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AU13" authorId="0" shapeId="0" xr:uid="{898E7CF5-B394-4965-9EE3-FF5FD061E3A1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:07</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AT14" authorId="0" shapeId="0" xr:uid="{DF014D67-CF6A-43AC-954D-E6FB7EDDB7BE}">
       <text>
         <r>
@@ -205,6 +233,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:06</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AU14" authorId="0" shapeId="0" xr:uid="{2CE6B8B2-360C-4600-9AAF-6A410ECF7F35}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
         </r>
       </text>
     </comment>
@@ -247,6 +289,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:06</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AU18" authorId="0" shapeId="0" xr:uid="{4E016ACA-9DF6-4810-B1D6-FBDBA28D6D84}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
         </r>
       </text>
     </comment>
@@ -373,6 +429,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:06</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AU22" authorId="0" shapeId="0" xr:uid="{2A155186-317C-45DB-8C50-DB02AF3532A9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
         </r>
       </text>
     </comment>
@@ -572,12 +642,40 @@
         </r>
       </text>
     </comment>
+    <comment ref="AU32" authorId="0" shapeId="0" xr:uid="{E41535A8-CF96-470F-9DD4-25017D65CC01}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AU34" authorId="0" shapeId="0" xr:uid="{F06C597E-7767-48F7-9EDB-4969A42CF1C1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:07</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -878,7 +976,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -905,6 +1003,7 @@
     <xf numFmtId="20" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1120,7 +1219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:AT34"/>
+  <dimension ref="A1:AV34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1138,10 +1237,10 @@
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
-    <col min="39" max="46" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="47" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AQ1">
         <f>COUNTA(AQ4:AQ34)</f>
         <v>31</v>
@@ -1158,8 +1257,12 @@
         <f>COUNTA(AT4:AT34)</f>
         <v>31</v>
       </c>
+      <c r="AU1">
+        <f>COUNTA(AU4:AU34)</f>
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" spans="1:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:48" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1298,8 +1401,11 @@
       <c r="AT3" s="5">
         <v>45069</v>
       </c>
+      <c r="AU3" s="5">
+        <v>45070</v>
+      </c>
     </row>
-    <row r="4" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1438,8 +1544,11 @@
       <c r="AT4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1578,8 +1687,11 @@
       <c r="AT5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1718,8 +1830,11 @@
       <c r="AT6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1858,8 +1973,11 @@
       <c r="AT7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1998,8 +2116,11 @@
       <c r="AT8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -2138,8 +2259,11 @@
       <c r="AT9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2278,8 +2402,12 @@
       <c r="AT10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV10" s="12"/>
     </row>
-    <row r="11" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -2418,8 +2546,11 @@
       <c r="AT11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2558,8 +2689,11 @@
       <c r="AT12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2698,8 +2832,11 @@
       <c r="AT13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2838,8 +2975,12 @@
       <c r="AT14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV14" s="12"/>
     </row>
-    <row r="15" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2978,8 +3119,11 @@
       <c r="AT15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -3118,8 +3262,11 @@
       <c r="AT16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -3258,8 +3405,11 @@
       <c r="AT17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -3398,8 +3548,12 @@
       <c r="AT18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV18" s="12"/>
     </row>
-    <row r="19" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -3538,8 +3692,11 @@
       <c r="AT19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU19" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="20" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -3678,8 +3835,11 @@
       <c r="AT20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -3818,8 +3978,11 @@
       <c r="AT21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -3958,8 +4121,12 @@
       <c r="AT22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV22" s="12"/>
     </row>
-    <row r="23" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -4098,8 +4265,11 @@
       <c r="AT23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -4238,8 +4408,11 @@
       <c r="AT24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -4378,8 +4551,11 @@
       <c r="AT25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -4518,8 +4694,11 @@
       <c r="AT26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -4658,8 +4837,11 @@
       <c r="AT27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -4798,8 +4980,11 @@
       <c r="AT28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -4938,8 +5123,11 @@
       <c r="AT29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -5078,8 +5266,11 @@
       <c r="AT30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -5218,8 +5409,11 @@
       <c r="AT31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -5358,8 +5552,12 @@
       <c r="AT32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV32" s="12"/>
     </row>
-    <row r="33" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -5498,8 +5696,11 @@
       <c r="AT33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AU33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -5636,6 +5837,9 @@
         <v>4</v>
       </c>
       <c r="AT34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE355A77-7742-4826-9AE3-C22C25991B1B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2B2240-F526-4F8A-96BF-CD0B46CACC93}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -250,6 +250,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AV14" authorId="0" shapeId="0" xr:uid="{54BF5ADE-B432-49CA-979B-A6810BEA4BBF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z18" authorId="0" shapeId="0" xr:uid="{08D2A270-552A-494A-8EB7-D7239F622756}">
       <text>
         <r>
@@ -303,6 +317,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:01</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AV18" authorId="0" shapeId="0" xr:uid="{F8733D7F-924C-4F52-BA98-FAAA3DA354F6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
         </r>
       </text>
     </comment>
@@ -446,6 +474,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AV22" authorId="0" shapeId="0" xr:uid="{313992C2-2CD1-4F63-86EB-415BAFCFEE7F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AR24" authorId="0" shapeId="0" xr:uid="{93A2F35A-C324-4F57-AAF5-D02DB505B765}">
       <text>
         <r>
@@ -457,6 +499,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:04</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AV24" authorId="0" shapeId="0" xr:uid="{11DE3918-BF98-438D-86FF-48BED784530A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:05</t>
         </r>
       </text>
     </comment>
@@ -656,6 +712,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AV32" authorId="0" shapeId="0" xr:uid="{655A9F47-4244-42FB-B2E1-AC159D15CB77}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AU34" authorId="0" shapeId="0" xr:uid="{F06C597E-7767-48F7-9EDB-4969A42CF1C1}">
       <text>
         <r>
@@ -675,7 +745,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1219,7 +1289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:AV34"/>
+  <dimension ref="A1:AW34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1237,32 +1307,16 @@
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
-    <col min="39" max="47" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="48" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AQ1">
-        <f>COUNTA(AQ4:AQ34)</f>
+    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AV1">
+        <f>COUNTA(AV4:AV34)</f>
         <v>31</v>
       </c>
-      <c r="AR1">
-        <f>COUNTA(AR4:AR34)</f>
-        <v>31</v>
-      </c>
-      <c r="AS1">
-        <f>COUNTA(AS4:AS34)</f>
-        <v>31</v>
-      </c>
-      <c r="AT1">
-        <f>COUNTA(AT4:AT34)</f>
-        <v>31</v>
-      </c>
-      <c r="AU1">
-        <f>COUNTA(AU4:AU34)</f>
-        <v>31</v>
-      </c>
     </row>
-    <row r="3" spans="1:48" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:49" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1404,8 +1458,11 @@
       <c r="AU3" s="5">
         <v>45070</v>
       </c>
+      <c r="AV3" s="5">
+        <v>45071</v>
+      </c>
     </row>
-    <row r="4" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1547,8 +1604,11 @@
       <c r="AU4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1690,8 +1750,11 @@
       <c r="AU5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1833,8 +1896,11 @@
       <c r="AU6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1976,8 +2042,11 @@
       <c r="AU7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2119,8 +2188,11 @@
       <c r="AU8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -2262,8 +2334,11 @@
       <c r="AU9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2405,9 +2480,11 @@
       <c r="AU10" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AV10" s="12"/>
+      <c r="AV10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -2549,8 +2626,11 @@
       <c r="AU11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2692,8 +2772,11 @@
       <c r="AU12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2835,8 +2918,11 @@
       <c r="AU13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2978,9 +3064,12 @@
       <c r="AU14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AV14" s="12"/>
+      <c r="AV14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW14" s="12"/>
     </row>
-    <row r="15" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -3122,8 +3211,11 @@
       <c r="AU15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -3265,8 +3357,11 @@
       <c r="AU16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -3408,8 +3503,11 @@
       <c r="AU17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -3551,9 +3649,12 @@
       <c r="AU18" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AV18" s="12"/>
+      <c r="AV18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW18" s="12"/>
     </row>
-    <row r="19" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -3695,8 +3796,11 @@
       <c r="AU19" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="AV19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -3838,8 +3942,11 @@
       <c r="AU20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -3981,8 +4088,11 @@
       <c r="AU21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -4124,9 +4234,12 @@
       <c r="AU22" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AV22" s="12"/>
+      <c r="AV22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW22" s="12"/>
     </row>
-    <row r="23" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -4268,8 +4381,11 @@
       <c r="AU23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -4411,8 +4527,11 @@
       <c r="AU24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -4554,8 +4673,11 @@
       <c r="AU25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -4697,8 +4819,11 @@
       <c r="AU26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -4840,8 +4965,11 @@
       <c r="AU27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -4983,8 +5111,11 @@
       <c r="AU28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -5126,8 +5257,11 @@
       <c r="AU29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -5269,8 +5403,11 @@
       <c r="AU30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -5412,8 +5549,11 @@
       <c r="AU31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -5555,9 +5695,12 @@
       <c r="AU32" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AV32" s="12"/>
+      <c r="AV32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW32" s="12"/>
     </row>
-    <row r="33" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -5699,8 +5842,11 @@
       <c r="AU33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AV33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -5840,6 +5986,9 @@
         <v>4</v>
       </c>
       <c r="AU34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2B2240-F526-4F8A-96BF-CD0B46CACC93}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6DF42D-7D99-47F5-8417-CE4D258D4253}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -745,7 +745,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1046,7 +1046,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1073,7 +1073,6 @@
     <xf numFmtId="20" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1307,12 +1306,12 @@
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
-    <col min="39" max="48" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="49" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="AV1">
-        <f>COUNTA(AV4:AV34)</f>
+      <c r="AW1">
+        <f>COUNTA(AW4:AW34)</f>
         <v>31</v>
       </c>
     </row>
@@ -1461,6 +1460,9 @@
       <c r="AV3" s="5">
         <v>45071</v>
       </c>
+      <c r="AW3" s="5">
+        <v>45072</v>
+      </c>
     </row>
     <row r="4" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
@@ -1607,6 +1609,9 @@
       <c r="AV4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
@@ -1753,6 +1758,9 @@
       <c r="AV5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
@@ -1899,6 +1907,9 @@
       <c r="AV6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
@@ -2043,6 +2054,9 @@
         <v>4</v>
       </c>
       <c r="AV7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW7" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2191,6 +2205,9 @@
       <c r="AV8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
@@ -2337,6 +2354,9 @@
       <c r="AV9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
@@ -2483,6 +2503,9 @@
       <c r="AV10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
@@ -2629,6 +2652,9 @@
       <c r="AV11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
@@ -2775,6 +2801,9 @@
       <c r="AV12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
@@ -2921,6 +2950,9 @@
       <c r="AV13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
@@ -3067,7 +3099,9 @@
       <c r="AV14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AW14" s="12"/>
+      <c r="AW14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
@@ -3214,6 +3248,9 @@
       <c r="AV15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
@@ -3360,6 +3397,9 @@
       <c r="AV16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
@@ -3506,6 +3546,9 @@
       <c r="AV17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
@@ -3652,7 +3695,9 @@
       <c r="AV18" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AW18" s="12"/>
+      <c r="AW18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="19" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
@@ -3799,6 +3844,9 @@
       <c r="AV19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="20" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
@@ -3945,6 +3993,9 @@
       <c r="AV20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
@@ -4091,6 +4142,9 @@
       <c r="AV21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
@@ -4237,7 +4291,9 @@
       <c r="AV22" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AW22" s="12"/>
+      <c r="AW22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
@@ -4384,6 +4440,9 @@
       <c r="AV23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="24" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
@@ -4530,6 +4589,9 @@
       <c r="AV24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="25" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
@@ -4676,6 +4738,9 @@
       <c r="AV25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="26" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
@@ -4822,6 +4887,9 @@
       <c r="AV26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="27" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
@@ -4968,6 +5036,9 @@
       <c r="AV27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
@@ -5114,6 +5185,9 @@
       <c r="AV28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="29" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
@@ -5260,6 +5334,9 @@
       <c r="AV29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="30" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
@@ -5406,6 +5483,9 @@
       <c r="AV30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
@@ -5552,6 +5632,9 @@
       <c r="AV31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
@@ -5698,9 +5781,11 @@
       <c r="AV32" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AW32" s="12"/>
+      <c r="AW32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -5845,8 +5930,11 @@
       <c r="AV33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AW33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -5989,6 +6077,9 @@
         <v>4</v>
       </c>
       <c r="AV34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6DF42D-7D99-47F5-8417-CE4D258D4253}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4380B0E5-9549-4B1A-9792-BA6455DF8FFC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,6 +81,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AY7" authorId="0" shapeId="0" xr:uid="{27F6C2AB-9FCF-44A6-BF7E-59206D098283}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AB10" authorId="0" shapeId="0" xr:uid="{3E374D75-3895-49F1-B346-BE43AE381426}">
       <text>
         <r>
@@ -134,6 +148,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:01</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AY10" authorId="0" shapeId="0" xr:uid="{DC77B05D-0DCC-4799-8A99-68BE55E4D395}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
         </r>
       </text>
     </comment>
@@ -334,6 +362,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AY18" authorId="0" shapeId="0" xr:uid="{E2E51B67-E3B6-493E-AA49-032BFF0D6B0C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="X20" authorId="0" shapeId="0" xr:uid="{DA902251-6155-45D0-BF90-7E5F5DFDE287}">
       <text>
         <r>
@@ -415,6 +457,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:04</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AY20" authorId="0" shapeId="0" xr:uid="{C29032D3-F767-4328-B618-DC5F3516234D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
         </r>
       </text>
     </comment>
@@ -745,7 +801,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1046,7 +1102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1073,6 +1129,7 @@
     <xf numFmtId="20" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1288,7 +1345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:AW34"/>
+  <dimension ref="A3:AZ34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1306,16 +1363,10 @@
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
-    <col min="39" max="49" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="51" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="AW1">
-        <f>COUNTA(AW4:AW34)</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:49" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:52" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1463,8 +1514,14 @@
       <c r="AW3" s="5">
         <v>45072</v>
       </c>
+      <c r="AX3" s="5">
+        <v>45073</v>
+      </c>
+      <c r="AY3" s="5">
+        <v>45075</v>
+      </c>
     </row>
-    <row r="4" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1612,8 +1669,14 @@
       <c r="AW4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1761,8 +1824,14 @@
       <c r="AW5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1910,8 +1979,14 @@
       <c r="AW6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2059,8 +2134,15 @@
       <c r="AW7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AZ7" s="12"/>
     </row>
-    <row r="8" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2208,8 +2290,14 @@
       <c r="AW8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -2357,8 +2445,14 @@
       <c r="AW9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AY9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2506,8 +2600,14 @@
       <c r="AW10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX10" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AY10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -2655,8 +2755,14 @@
       <c r="AW11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2804,8 +2910,14 @@
       <c r="AW12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2953,8 +3065,14 @@
       <c r="AW13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -3102,8 +3220,14 @@
       <c r="AW14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -3251,8 +3375,14 @@
       <c r="AW15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -3400,8 +3530,14 @@
       <c r="AW16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -3549,8 +3685,14 @@
       <c r="AW17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -3698,8 +3840,14 @@
       <c r="AW18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -3847,8 +3995,14 @@
       <c r="AW19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX19" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AY19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -3996,8 +4150,14 @@
       <c r="AW20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -4145,8 +4305,14 @@
       <c r="AW21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -4294,8 +4460,14 @@
       <c r="AW22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -4443,8 +4615,14 @@
       <c r="AW23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -4592,8 +4770,14 @@
       <c r="AW24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -4741,8 +4925,14 @@
       <c r="AW25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -4890,8 +5080,14 @@
       <c r="AW26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX26" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AY26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -5039,8 +5235,14 @@
       <c r="AW27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX27" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AY27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -5188,8 +5390,14 @@
       <c r="AW28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX28" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -5337,8 +5545,14 @@
       <c r="AW29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -5486,8 +5700,14 @@
       <c r="AW30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -5635,8 +5855,14 @@
       <c r="AW31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -5784,8 +6010,14 @@
       <c r="AW32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -5933,8 +6165,14 @@
       <c r="AW33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AX33" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -6080,6 +6318,12 @@
         <v>4</v>
       </c>
       <c r="AW34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4380B0E5-9549-4B1A-9792-BA6455DF8FFC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FF413B-34F2-471B-8362-7BC8BEF9266B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,6 +92,21 @@
             <charset val="1"/>
           </rPr>
           <t>09:01</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AZ7" authorId="0" shapeId="0" xr:uid="{C90C8130-F593-496A-B9EB-C227ABABC7D2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:14
+Forgot ID card</t>
         </r>
       </text>
     </comment>
@@ -572,6 +587,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="AZ24" authorId="0" shapeId="0" xr:uid="{D369D67F-6F83-4C54-869D-89F58B5FA647}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R25" authorId="0" shapeId="0" xr:uid="{2E3360AC-93ED-47D5-A29A-768ED91910D3}">
       <text>
         <r>
@@ -801,7 +830,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1102,7 +1131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1129,7 +1158,6 @@
     <xf numFmtId="20" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1345,7 +1373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:AZ34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1363,9 +1391,15 @@
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
-    <col min="39" max="51" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="52" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="AZ1">
+        <f>COUNTA(AZ4:AZ34)</f>
+        <v>31</v>
+      </c>
+    </row>
     <row r="3" spans="1:52" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
@@ -1519,6 +1553,9 @@
       </c>
       <c r="AY3" s="5">
         <v>45075</v>
+      </c>
+      <c r="AZ3" s="5">
+        <v>45076</v>
       </c>
     </row>
     <row r="4" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1675,6 +1712,9 @@
       <c r="AY4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
@@ -1830,6 +1870,9 @@
       <c r="AY5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
@@ -1985,6 +2028,9 @@
       <c r="AY6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
@@ -2140,7 +2186,9 @@
       <c r="AY7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AZ7" s="12"/>
+      <c r="AZ7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
@@ -2296,6 +2344,9 @@
       <c r="AY8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
@@ -2451,6 +2502,9 @@
       <c r="AY9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
@@ -2606,6 +2660,9 @@
       <c r="AY10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
@@ -2761,6 +2818,9 @@
       <c r="AY11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
@@ -2916,6 +2976,9 @@
       <c r="AY12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
@@ -3071,6 +3134,9 @@
       <c r="AY13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
@@ -3226,6 +3292,9 @@
       <c r="AY14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
@@ -3381,6 +3450,9 @@
       <c r="AY15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
@@ -3536,8 +3608,11 @@
       <c r="AY16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -3691,8 +3766,11 @@
       <c r="AY17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -3846,8 +3924,11 @@
       <c r="AY18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -4001,8 +4082,11 @@
       <c r="AY19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -4156,8 +4240,11 @@
       <c r="AY20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -4311,8 +4398,11 @@
       <c r="AY21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -4466,8 +4556,11 @@
       <c r="AY22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -4621,8 +4714,11 @@
       <c r="AY23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -4776,8 +4872,11 @@
       <c r="AY24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -4931,8 +5030,11 @@
       <c r="AY25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -5086,8 +5188,11 @@
       <c r="AY26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -5241,8 +5346,11 @@
       <c r="AY27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -5396,8 +5504,11 @@
       <c r="AY28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -5551,8 +5662,11 @@
       <c r="AY29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -5706,8 +5820,11 @@
       <c r="AY30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -5861,8 +5978,11 @@
       <c r="AY31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -6016,8 +6136,11 @@
       <c r="AY32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -6171,8 +6294,11 @@
       <c r="AY33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="AZ33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -6324,6 +6450,9 @@
         <v>4</v>
       </c>
       <c r="AY34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AZ34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FF413B-34F2-471B-8362-7BC8BEF9266B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE95585A-AF06-44F0-9047-010EBEB84ECA}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,6 +107,21 @@
           </rPr>
           <t>09:14
 Forgot ID card</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BA7" authorId="0" shapeId="0" xr:uid="{73BAE9C2-15B6-400E-BB42-221462569965}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>12:16
+Did not get Auto</t>
         </r>
       </text>
     </comment>
@@ -262,6 +277,21 @@
             <charset val="1"/>
           </rPr>
           <t>09:07</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BA13" authorId="0" shapeId="0" xr:uid="{3C5F30F2-003D-47E1-AFAA-4AE0DAC07959}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>12:16
+Did not get Auto</t>
         </r>
       </text>
     </comment>
@@ -830,7 +860,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1373,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A3:BA34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1391,16 +1421,10 @@
     <col min="28" max="34" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
-    <col min="39" max="52" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="AZ1">
-        <f>COUNTA(AZ4:AZ34)</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:52" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:53" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1557,8 +1581,11 @@
       <c r="AZ3" s="5">
         <v>45076</v>
       </c>
+      <c r="BA3" s="5">
+        <v>45076</v>
+      </c>
     </row>
-    <row r="4" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1715,8 +1742,11 @@
       <c r="AZ4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1873,8 +1903,11 @@
       <c r="AZ5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2031,8 +2064,11 @@
       <c r="AZ6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2189,8 +2225,11 @@
       <c r="AZ7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2347,8 +2386,11 @@
       <c r="AZ8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA8" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="9" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -2505,8 +2547,11 @@
       <c r="AZ9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2663,8 +2708,11 @@
       <c r="AZ10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -2821,8 +2869,11 @@
       <c r="AZ11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2979,8 +3030,11 @@
       <c r="AZ12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -3137,8 +3191,11 @@
       <c r="AZ13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -3295,8 +3352,11 @@
       <c r="AZ14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -3453,8 +3513,11 @@
       <c r="AZ15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -3611,8 +3674,11 @@
       <c r="AZ16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -3769,8 +3835,11 @@
       <c r="AZ17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -3927,8 +3996,11 @@
       <c r="AZ18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -4085,8 +4157,11 @@
       <c r="AZ19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -4243,8 +4318,11 @@
       <c r="AZ20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -4401,8 +4479,11 @@
       <c r="AZ21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -4559,8 +4640,11 @@
       <c r="AZ22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -4717,8 +4801,11 @@
       <c r="AZ23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -4875,8 +4962,11 @@
       <c r="AZ24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -5033,8 +5123,11 @@
       <c r="AZ25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -5191,8 +5284,11 @@
       <c r="AZ26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -5349,8 +5445,11 @@
       <c r="AZ27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -5507,8 +5606,11 @@
       <c r="AZ28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -5665,8 +5767,11 @@
       <c r="AZ29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -5823,8 +5928,11 @@
       <c r="AZ30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -5981,8 +6089,11 @@
       <c r="AZ31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -6139,8 +6250,11 @@
       <c r="AZ32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -6297,8 +6411,11 @@
       <c r="AZ33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BA33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -6453,6 +6570,9 @@
         <v>4</v>
       </c>
       <c r="AZ34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BA34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE95585A-AF06-44F0-9047-010EBEB84ECA}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C5D66F-4774-4C58-B72E-9AD00B8FB569}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -743,6 +743,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BB25" authorId="0" shapeId="0" xr:uid="{8A722040-D422-45F1-9CC7-67C08214BD53}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AS27" authorId="0" shapeId="0" xr:uid="{E3CE2C02-3FD9-4256-B1DE-A8BDC78C9795}">
       <text>
         <r>
@@ -860,7 +874,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1403,7 +1417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A3:BA34"/>
+  <dimension ref="A1:BB34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1422,9 +1436,16 @@
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
     <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:53" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BB1">
+        <f>COUNTA(BB4:BB34)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1584,8 +1605,11 @@
       <c r="BA3" s="5">
         <v>45076</v>
       </c>
+      <c r="BB3" s="5">
+        <v>45078</v>
+      </c>
     </row>
-    <row r="4" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1745,8 +1769,11 @@
       <c r="BA4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1906,8 +1933,11 @@
       <c r="BA5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2067,8 +2097,11 @@
       <c r="BA6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2228,8 +2261,11 @@
       <c r="BA7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2389,8 +2425,11 @@
       <c r="BA8" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="BB8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -2550,8 +2589,11 @@
       <c r="BA9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2711,8 +2753,11 @@
       <c r="BA10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -2872,8 +2917,11 @@
       <c r="BA11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -3033,8 +3081,11 @@
       <c r="BA12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -3194,8 +3245,11 @@
       <c r="BA13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -3355,8 +3409,11 @@
       <c r="BA14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -3516,8 +3573,11 @@
       <c r="BA15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -3677,8 +3737,11 @@
       <c r="BA16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -3838,8 +3901,11 @@
       <c r="BA17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -3999,8 +4065,11 @@
       <c r="BA18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -4160,8 +4229,11 @@
       <c r="BA19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -4321,8 +4393,11 @@
       <c r="BA20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -4482,8 +4557,11 @@
       <c r="BA21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -4643,8 +4721,11 @@
       <c r="BA22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -4804,8 +4885,11 @@
       <c r="BA23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -4965,8 +5049,11 @@
       <c r="BA24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -5126,8 +5213,11 @@
       <c r="BA25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -5287,8 +5377,11 @@
       <c r="BA26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -5448,8 +5541,11 @@
       <c r="BA27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -5609,8 +5705,11 @@
       <c r="BA28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -5770,8 +5869,11 @@
       <c r="BA29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -5931,8 +6033,11 @@
       <c r="BA30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -6092,8 +6197,11 @@
       <c r="BA31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -6253,8 +6361,11 @@
       <c r="BA32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -6414,8 +6525,11 @@
       <c r="BA33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BB33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -6573,6 +6687,9 @@
         <v>4</v>
       </c>
       <c r="BA34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BB34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C5D66F-4774-4C58-B72E-9AD00B8FB569}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53109F44-083B-41B2-8EF0-1DAD43165ED4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -874,7 +874,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1417,7 +1417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:BB34"/>
+  <dimension ref="A1:BC34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1436,16 +1436,16 @@
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
     <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="54" max="55" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="BB1">
-        <f>COUNTA(BB4:BB34)</f>
+    <row r="1" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BC1">
+        <f>COUNTA(BC4:BC34)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:54" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:55" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1608,8 +1608,11 @@
       <c r="BB3" s="5">
         <v>45078</v>
       </c>
+      <c r="BC3" s="5">
+        <v>45079</v>
+      </c>
     </row>
-    <row r="4" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1772,8 +1775,11 @@
       <c r="BB4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1936,8 +1942,11 @@
       <c r="BB5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2100,8 +2109,11 @@
       <c r="BB6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2264,8 +2276,11 @@
       <c r="BB7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2428,8 +2443,11 @@
       <c r="BB8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -2592,8 +2610,11 @@
       <c r="BB9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2756,8 +2777,11 @@
       <c r="BB10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -2920,8 +2944,11 @@
       <c r="BB11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -3084,8 +3111,11 @@
       <c r="BB12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -3248,8 +3278,11 @@
       <c r="BB13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -3412,8 +3445,11 @@
       <c r="BB14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -3576,8 +3612,11 @@
       <c r="BB15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -3740,8 +3779,11 @@
       <c r="BB16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -3904,8 +3946,11 @@
       <c r="BB17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -4068,8 +4113,11 @@
       <c r="BB18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -4232,8 +4280,11 @@
       <c r="BB19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -4396,8 +4447,11 @@
       <c r="BB20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -4560,8 +4614,11 @@
       <c r="BB21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -4724,8 +4781,11 @@
       <c r="BB22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -4888,8 +4948,11 @@
       <c r="BB23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -5052,8 +5115,11 @@
       <c r="BB24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -5216,8 +5282,11 @@
       <c r="BB25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -5380,8 +5449,11 @@
       <c r="BB26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -5544,8 +5616,11 @@
       <c r="BB27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -5708,8 +5783,11 @@
       <c r="BB28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -5872,8 +5950,11 @@
       <c r="BB29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -6036,8 +6117,11 @@
       <c r="BB30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -6200,8 +6284,11 @@
       <c r="BB31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -6364,8 +6451,11 @@
       <c r="BB32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -6528,8 +6618,11 @@
       <c r="BB33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BC33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -6690,6 +6783,9 @@
         <v>4</v>
       </c>
       <c r="BB34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BC34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53109F44-083B-41B2-8EF0-1DAD43165ED4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5695DBF7-4FB7-40D5-8EDB-53964E370617}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -519,6 +519,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BE20" authorId="0" shapeId="0" xr:uid="{28872B74-907F-4CB4-A52A-C076BA204676}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:03</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z22" authorId="0" shapeId="0" xr:uid="{DDD8C7AD-47C9-4E11-8FE8-07117ACB2789}">
       <text>
         <r>
@@ -589,6 +603,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BE22" authorId="0" shapeId="0" xr:uid="{D586A740-2E86-4B20-9CDB-7CD87AA72FCD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:08</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AR24" authorId="0" shapeId="0" xr:uid="{93A2F35A-C324-4F57-AAF5-D02DB505B765}">
       <text>
         <r>
@@ -628,6 +656,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:04</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BE24" authorId="0" shapeId="0" xr:uid="{23C3DE8E-3B6D-4BB3-BE00-B7C70C3B8B0C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:07</t>
         </r>
       </text>
     </comment>
@@ -757,6 +799,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BE25" authorId="0" shapeId="0" xr:uid="{C894E248-ACE6-489A-BB4A-523D37CB9DE3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:10</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AS27" authorId="0" shapeId="0" xr:uid="{E3CE2C02-3FD9-4256-B1DE-A8BDC78C9795}">
       <text>
         <r>
@@ -874,7 +930,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1417,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:BC34"/>
+  <dimension ref="A1:BE34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1436,16 +1492,16 @@
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
     <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="54" max="55" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="54" max="57" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="BC1">
-        <f>COUNTA(BC4:BC34)</f>
+    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BE1">
+        <f>COUNTA(BE4:BE34)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:55" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:57" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1603,7 +1659,7 @@
         <v>45076</v>
       </c>
       <c r="BA3" s="5">
-        <v>45076</v>
+        <v>45077</v>
       </c>
       <c r="BB3" s="5">
         <v>45078</v>
@@ -1611,8 +1667,14 @@
       <c r="BC3" s="5">
         <v>45079</v>
       </c>
+      <c r="BD3" s="5">
+        <v>45080</v>
+      </c>
+      <c r="BE3" s="5">
+        <v>45082</v>
+      </c>
     </row>
-    <row r="4" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1778,8 +1840,14 @@
       <c r="BC4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="BE4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1945,8 +2013,14 @@
       <c r="BC5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2112,8 +2186,14 @@
       <c r="BC6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2279,8 +2359,14 @@
       <c r="BC7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2446,8 +2532,14 @@
       <c r="BC8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -2613,8 +2705,14 @@
       <c r="BC9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2780,8 +2878,14 @@
       <c r="BC10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -2947,8 +3051,14 @@
       <c r="BC11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -3114,8 +3224,14 @@
       <c r="BC12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -3281,8 +3397,14 @@
       <c r="BC13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -3448,8 +3570,14 @@
       <c r="BC14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="BE14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -3615,8 +3743,14 @@
       <c r="BC15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -3782,8 +3916,14 @@
       <c r="BC16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -3949,8 +4089,14 @@
       <c r="BC17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -4116,8 +4262,14 @@
       <c r="BC18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -4283,8 +4435,14 @@
       <c r="BC19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -4450,8 +4608,14 @@
       <c r="BC20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -4617,8 +4781,14 @@
       <c r="BC21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -4784,8 +4954,14 @@
       <c r="BC22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -4951,8 +5127,14 @@
       <c r="BC23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -5118,8 +5300,14 @@
       <c r="BC24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -5285,8 +5473,14 @@
       <c r="BC25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -5452,8 +5646,14 @@
       <c r="BC26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -5619,8 +5819,14 @@
       <c r="BC27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -5786,8 +5992,14 @@
       <c r="BC28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD28" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -5953,8 +6165,14 @@
       <c r="BC29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -6120,8 +6338,14 @@
       <c r="BC30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -6287,8 +6511,14 @@
       <c r="BC31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -6454,8 +6684,14 @@
       <c r="BC32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -6621,8 +6857,14 @@
       <c r="BC33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BD33" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -6786,6 +7028,12 @@
         <v>4</v>
       </c>
       <c r="BC34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BD34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5695DBF7-4FB7-40D5-8EDB-53964E370617}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FBA3A3-08B1-4FD1-812E-669B934BE971}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -337,6 +337,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BF14" authorId="0" shapeId="0" xr:uid="{9FF06717-6F1A-450B-A299-DAAD69E407EB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:05</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z18" authorId="0" shapeId="0" xr:uid="{08D2A270-552A-494A-8EB7-D7239F622756}">
       <text>
         <r>
@@ -418,6 +432,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:02</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BF18" authorId="0" shapeId="0" xr:uid="{2D1B66A1-CBEA-4998-9519-8F8198AEDE21}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:05</t>
         </r>
       </text>
     </comment>
@@ -617,6 +645,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BF22" authorId="0" shapeId="0" xr:uid="{11754A03-B043-4C78-82CA-CC1FEE479723}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:05</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AR24" authorId="0" shapeId="0" xr:uid="{93A2F35A-C324-4F57-AAF5-D02DB505B765}">
       <text>
         <r>
@@ -813,6 +855,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BF25" authorId="0" shapeId="0" xr:uid="{12AD4DFF-52F8-492C-8D73-6F71D213E506}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:30</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AS27" authorId="0" shapeId="0" xr:uid="{E3CE2C02-3FD9-4256-B1DE-A8BDC78C9795}">
       <text>
         <r>
@@ -911,6 +967,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BF32" authorId="0" shapeId="0" xr:uid="{0A132B22-9355-4162-BB58-4CDA2752AE16}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:05</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AU34" authorId="0" shapeId="0" xr:uid="{F06C597E-7767-48F7-9EDB-4969A42CF1C1}">
       <text>
         <r>
@@ -930,7 +1000,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1473,7 +1543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:BE34"/>
+  <dimension ref="A1:BF34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1492,16 +1562,16 @@
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
     <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="54" max="57" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="54" max="58" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="BE1">
-        <f>COUNTA(BE4:BE34)</f>
+    <row r="1" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BF1">
+        <f>COUNTA(BF4:BF34)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:57" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:58" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1673,8 +1743,11 @@
       <c r="BE3" s="5">
         <v>45082</v>
       </c>
+      <c r="BF3" s="5">
+        <v>45083</v>
+      </c>
     </row>
-    <row r="4" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1846,8 +1919,11 @@
       <c r="BE4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2019,8 +2095,11 @@
       <c r="BE5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2192,8 +2271,11 @@
       <c r="BE6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2365,8 +2447,11 @@
       <c r="BE7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2538,8 +2623,11 @@
       <c r="BE8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -2711,8 +2799,11 @@
       <c r="BE9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2884,8 +2975,11 @@
       <c r="BE10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -3057,8 +3151,11 @@
       <c r="BE11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -3230,8 +3327,11 @@
       <c r="BE12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -3403,8 +3503,11 @@
       <c r="BE13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -3576,8 +3679,11 @@
       <c r="BE14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -3749,8 +3855,11 @@
       <c r="BE15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -3922,8 +4031,11 @@
       <c r="BE16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -4095,8 +4207,11 @@
       <c r="BE17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -4268,8 +4383,11 @@
       <c r="BE18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -4441,8 +4559,11 @@
       <c r="BE19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -4614,8 +4735,11 @@
       <c r="BE20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -4787,8 +4911,11 @@
       <c r="BE21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -4960,8 +5087,11 @@
       <c r="BE22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -5133,8 +5263,11 @@
       <c r="BE23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -5306,8 +5439,11 @@
       <c r="BE24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -5479,8 +5615,11 @@
       <c r="BE25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -5652,8 +5791,11 @@
       <c r="BE26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -5825,8 +5967,11 @@
       <c r="BE27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -5998,8 +6143,11 @@
       <c r="BE28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -6171,8 +6319,11 @@
       <c r="BE29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -6344,8 +6495,11 @@
       <c r="BE30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -6517,8 +6671,11 @@
       <c r="BE31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -6690,8 +6847,11 @@
       <c r="BE32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -6863,8 +7023,11 @@
       <c r="BE33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BF33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -7034,6 +7197,9 @@
         <v>4</v>
       </c>
       <c r="BE34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BF34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FBA3A3-08B1-4FD1-812E-669B934BE971}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86441AFA-0983-47B0-BC65-6D8427754895}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -122,6 +122,20 @@
           </rPr>
           <t>12:16
 Did not get Auto</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BG7" authorId="0" shapeId="0" xr:uid="{C80B1CC6-A479-429C-9DBE-89736C592C11}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:08</t>
         </r>
       </text>
     </comment>
@@ -292,6 +306,20 @@
           </rPr>
           <t>12:16
 Did not get Auto</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BG13" authorId="0" shapeId="0" xr:uid="{278C75D3-DC24-47BD-B62D-53741EA37762}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04</t>
         </r>
       </text>
     </comment>
@@ -911,6 +939,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BG30" authorId="0" shapeId="0" xr:uid="{1034DF53-6D02-4B5E-9C70-941425DFBFEA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z32" authorId="0" shapeId="0" xr:uid="{59E0B9C2-F2EA-4082-81B3-59239B204C71}">
       <text>
         <r>
@@ -995,12 +1037,26 @@
         </r>
       </text>
     </comment>
+    <comment ref="BG34" authorId="0" shapeId="0" xr:uid="{5256F25A-6F19-4E8B-891B-BC62926229B8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1543,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:BF34"/>
+  <dimension ref="A1:BG34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1562,16 +1618,16 @@
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
     <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="54" max="58" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="54" max="59" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" x14ac:dyDescent="0.25">
-      <c r="BF1">
-        <f>COUNTA(BF4:BF34)</f>
+    <row r="1" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BG1">
+        <f>COUNTA(BG4:BG34)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:58" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:59" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1746,8 +1802,11 @@
       <c r="BF3" s="5">
         <v>45083</v>
       </c>
+      <c r="BG3" s="5">
+        <v>45084</v>
+      </c>
     </row>
-    <row r="4" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1922,8 +1981,11 @@
       <c r="BF4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2098,8 +2160,11 @@
       <c r="BF5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2274,8 +2339,11 @@
       <c r="BF6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2450,8 +2518,11 @@
       <c r="BF7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2626,8 +2697,11 @@
       <c r="BF8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -2802,8 +2876,11 @@
       <c r="BF9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2978,8 +3055,11 @@
       <c r="BF10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -3154,8 +3234,11 @@
       <c r="BF11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -3330,8 +3413,11 @@
       <c r="BF12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -3506,8 +3592,11 @@
       <c r="BF13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -3682,8 +3771,11 @@
       <c r="BF14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -3858,8 +3950,11 @@
       <c r="BF15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -4034,8 +4129,11 @@
       <c r="BF16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -4210,8 +4308,11 @@
       <c r="BF17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -4386,8 +4487,11 @@
       <c r="BF18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -4562,8 +4666,11 @@
       <c r="BF19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -4738,8 +4845,11 @@
       <c r="BF20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -4914,8 +5024,11 @@
       <c r="BF21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -5090,8 +5203,11 @@
       <c r="BF22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -5266,8 +5382,11 @@
       <c r="BF23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -5442,8 +5561,11 @@
       <c r="BF24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -5618,8 +5740,11 @@
       <c r="BF25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -5794,8 +5919,11 @@
       <c r="BF26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -5970,8 +6098,11 @@
       <c r="BF27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -6146,8 +6277,11 @@
       <c r="BF28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -6322,8 +6456,11 @@
       <c r="BF29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -6498,8 +6635,11 @@
       <c r="BF30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -6674,8 +6814,11 @@
       <c r="BF31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -6850,8 +6993,11 @@
       <c r="BF32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -7026,8 +7172,11 @@
       <c r="BF33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BG33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -7200,6 +7349,9 @@
         <v>4</v>
       </c>
       <c r="BF34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BG34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86441AFA-0983-47B0-BC65-6D8427754895}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA71CA73-02DA-46BB-AD06-42D4642F8F08}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -379,6 +379,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BH14" authorId="0" shapeId="0" xr:uid="{99628795-6873-4B90-B578-54C34A08FC98}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:03</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z18" authorId="0" shapeId="0" xr:uid="{08D2A270-552A-494A-8EB7-D7239F622756}">
       <text>
         <r>
@@ -477,6 +491,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BH18" authorId="0" shapeId="0" xr:uid="{6C235A7D-E0BA-4ABC-9121-209483C36A0C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:03</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="X20" authorId="0" shapeId="0" xr:uid="{DA902251-6155-45D0-BF90-7E5F5DFDE287}">
       <text>
         <r>
@@ -687,6 +715,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BH22" authorId="0" shapeId="0" xr:uid="{90C7F6D7-95C2-402A-832D-6D722DC3954E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:03</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AR24" authorId="0" shapeId="0" xr:uid="{93A2F35A-C324-4F57-AAF5-D02DB505B765}">
       <text>
         <r>
@@ -1020,6 +1062,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:05</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BH32" authorId="0" shapeId="0" xr:uid="{E356E62C-083F-4A32-A7C3-7A9C63038977}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:03</t>
         </r>
       </text>
     </comment>
@@ -1056,7 +1112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1599,7 +1655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:BG34"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1618,16 +1674,16 @@
     <col min="35" max="37" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
     <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="54" max="59" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="54" max="60" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" x14ac:dyDescent="0.25">
-      <c r="BG1">
-        <f>COUNTA(BG4:BG34)</f>
+    <row r="1" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BH1">
+        <f>COUNTA(BH4:BH34)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:59" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:60" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1805,8 +1861,11 @@
       <c r="BG3" s="5">
         <v>45084</v>
       </c>
+      <c r="BH3" s="5">
+        <v>45085</v>
+      </c>
     </row>
-    <row r="4" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1984,8 +2043,11 @@
       <c r="BG4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2163,8 +2225,11 @@
       <c r="BG5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2342,8 +2407,11 @@
       <c r="BG6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2521,8 +2589,11 @@
       <c r="BG7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2700,8 +2771,11 @@
       <c r="BG8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -2879,8 +2953,11 @@
       <c r="BG9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -3058,8 +3135,11 @@
       <c r="BG10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -3237,8 +3317,11 @@
       <c r="BG11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -3416,8 +3499,11 @@
       <c r="BG12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -3595,8 +3681,11 @@
       <c r="BG13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -3774,8 +3863,11 @@
       <c r="BG14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -3953,8 +4045,11 @@
       <c r="BG15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -4132,8 +4227,11 @@
       <c r="BG16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -4311,8 +4409,11 @@
       <c r="BG17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -4490,8 +4591,11 @@
       <c r="BG18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -4669,8 +4773,11 @@
       <c r="BG19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -4848,8 +4955,11 @@
       <c r="BG20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -5027,8 +5137,11 @@
       <c r="BG21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="BG22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -5385,8 +5501,11 @@
       <c r="BG23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -5564,8 +5683,11 @@
       <c r="BG24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -5743,8 +5865,11 @@
       <c r="BG25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -5922,8 +6047,11 @@
       <c r="BG26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -6101,8 +6229,11 @@
       <c r="BG27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -6280,8 +6411,11 @@
       <c r="BG28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -6459,8 +6593,11 @@
       <c r="BG29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -6638,8 +6775,11 @@
       <c r="BG30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -6817,8 +6957,11 @@
       <c r="BG31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -6996,8 +7139,11 @@
       <c r="BG32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -7175,8 +7321,11 @@
       <c r="BG33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BH33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -7352,6 +7501,9 @@
         <v>4</v>
       </c>
       <c r="BG34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BH34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F595E9-4A75-4578-985C-615FDBF857D7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8DA398-0C78-4FC4-9FD0-F6A083EB991F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,6 +39,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BJ5" authorId="0" shapeId="0" xr:uid="{A969E27A-BCFB-4511-8EE1-E76352DE5C6D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:03</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="N7" authorId="0" shapeId="0" xr:uid="{F6F4F720-DA46-4DC0-8124-2D3953156CC6}">
       <text>
         <r>
@@ -505,6 +519,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BJ19" authorId="0" shapeId="0" xr:uid="{48F35BF0-9CB9-4D81-AF45-B901F733BC15}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:07</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="X20" authorId="0" shapeId="0" xr:uid="{DA902251-6155-45D0-BF90-7E5F5DFDE287}">
       <text>
         <r>
@@ -978,6 +1006,20 @@
             <charset val="1"/>
           </rPr>
           <t>9:02</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BJ29" authorId="0" shapeId="0" xr:uid="{97D24932-3ACB-4A00-91DF-1AC3DB11CEDA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:03</t>
         </r>
       </text>
     </comment>
@@ -1126,7 +1168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1669,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:BI34"/>
+  <dimension ref="A1:BJ34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1689,15 +1731,16 @@
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
     <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="54" max="61" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" x14ac:dyDescent="0.25">
-      <c r="BI1">
-        <f>COUNTA(BI4:BI34)</f>
+    <row r="1" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BJ1">
+        <f>COUNTA(BJ4:BJ34)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:61" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:62" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1881,8 +1924,11 @@
       <c r="BI3" s="5">
         <v>45086</v>
       </c>
+      <c r="BJ3" s="5">
+        <v>45087</v>
+      </c>
     </row>
-    <row r="4" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2066,8 +2112,11 @@
       <c r="BI4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2251,8 +2300,11 @@
       <c r="BI5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2436,8 +2488,11 @@
       <c r="BI6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2621,8 +2676,11 @@
       <c r="BI7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2806,8 +2864,11 @@
       <c r="BI8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -2991,8 +3052,11 @@
       <c r="BI9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -3176,8 +3240,11 @@
       <c r="BI10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -3361,8 +3428,11 @@
       <c r="BI11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -3546,8 +3616,11 @@
       <c r="BI12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -3731,8 +3804,11 @@
       <c r="BI13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -3916,8 +3992,11 @@
       <c r="BI14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -4101,8 +4180,11 @@
       <c r="BI15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -4286,8 +4368,11 @@
       <c r="BI16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ16" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="17" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -4471,8 +4556,11 @@
       <c r="BI17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -4656,8 +4744,11 @@
       <c r="BI18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -4841,8 +4932,11 @@
       <c r="BI19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -5026,8 +5120,11 @@
       <c r="BI20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -5211,8 +5308,11 @@
       <c r="BI21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -5396,8 +5496,11 @@
       <c r="BI22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ22" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="23" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -5581,8 +5684,11 @@
       <c r="BI23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -5766,8 +5872,11 @@
       <c r="BI24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -5951,8 +6060,11 @@
       <c r="BI25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -6136,8 +6248,11 @@
       <c r="BI26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -6321,8 +6436,11 @@
       <c r="BI27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -6506,8 +6624,11 @@
       <c r="BI28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -6691,8 +6812,11 @@
       <c r="BI29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -6876,8 +7000,11 @@
       <c r="BI30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -7061,8 +7188,11 @@
       <c r="BI31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -7246,8 +7376,11 @@
       <c r="BI32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -7431,8 +7564,11 @@
       <c r="BI33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BJ33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -7614,6 +7750,9 @@
         <v>4</v>
       </c>
       <c r="BI34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8DA398-0C78-4FC4-9FD0-F6A083EB991F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F463D970-8C2C-4814-850F-2437E0A9B629}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -223,6 +223,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BK10" authorId="0" shapeId="0" xr:uid="{94E351C1-F5CF-4DA9-91AC-07AEEF67C43D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AR12" authorId="0" shapeId="0" xr:uid="{545F614C-5FF6-474D-A0CA-692648A0BE68}">
       <text>
         <r>
@@ -824,6 +838,21 @@
             <charset val="1"/>
           </rPr>
           <t>09:02</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BK24" authorId="0" shapeId="0" xr:uid="{9B653D14-1C04-45BF-B9BC-DC7021306FEA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04
+He came in rain with full of water. But still tried to reach on time</t>
         </r>
       </text>
     </comment>
@@ -1168,7 +1197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1711,7 +1740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:BJ34"/>
+  <dimension ref="A1:BK34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1731,16 +1760,16 @@
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
     <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="54" max="61" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="62" max="63" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="BJ1">
-        <f>COUNTA(BJ4:BJ34)</f>
+    <row r="1" spans="1:63" x14ac:dyDescent="0.25">
+      <c r="BK1">
+        <f>COUNTA(BK4:BK34)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:62" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:63" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1927,8 +1956,11 @@
       <c r="BJ3" s="5">
         <v>45087</v>
       </c>
+      <c r="BK3" s="5">
+        <v>45089</v>
+      </c>
     </row>
-    <row r="4" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2115,8 +2147,11 @@
       <c r="BJ4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2303,8 +2338,11 @@
       <c r="BJ5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2491,8 +2529,11 @@
       <c r="BJ6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2679,8 +2720,11 @@
       <c r="BJ7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2867,8 +2911,11 @@
       <c r="BJ8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -3055,8 +3102,11 @@
       <c r="BJ9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -3243,8 +3293,11 @@
       <c r="BJ10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -3431,8 +3484,11 @@
       <c r="BJ11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -3619,8 +3675,11 @@
       <c r="BJ12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -3807,8 +3866,11 @@
       <c r="BJ13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -3995,8 +4057,11 @@
       <c r="BJ14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -4183,8 +4248,11 @@
       <c r="BJ15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -4371,8 +4439,11 @@
       <c r="BJ16" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="BK16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -4559,8 +4630,11 @@
       <c r="BJ17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -4747,8 +4821,11 @@
       <c r="BJ18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -4935,8 +5012,11 @@
       <c r="BJ19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK19" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="20" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -5123,8 +5203,11 @@
       <c r="BJ20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -5311,8 +5394,11 @@
       <c r="BJ21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -5499,8 +5585,11 @@
       <c r="BJ22" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="BK22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -5687,8 +5776,11 @@
       <c r="BJ23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -5875,8 +5967,11 @@
       <c r="BJ24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -6063,8 +6158,11 @@
       <c r="BJ25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -6251,8 +6349,11 @@
       <c r="BJ26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -6439,8 +6540,11 @@
       <c r="BJ27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -6627,8 +6731,11 @@
       <c r="BJ28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -6815,8 +6922,11 @@
       <c r="BJ29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -7003,8 +7113,11 @@
       <c r="BJ30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -7191,8 +7304,11 @@
       <c r="BJ31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -7379,8 +7495,11 @@
       <c r="BJ32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -7567,8 +7686,11 @@
       <c r="BJ33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BK33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -7753,6 +7875,9 @@
         <v>4</v>
       </c>
       <c r="BJ34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BK34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F463D970-8C2C-4814-850F-2437E0A9B629}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44064D41-A950-4D3D-89A3-2F31593C932A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -659,6 +659,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BL20" authorId="0" shapeId="0" xr:uid="{3C9041CD-A5B4-42E1-BAE2-602CBF20F658}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:05</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z22" authorId="0" shapeId="0" xr:uid="{DDD8C7AD-47C9-4E11-8FE8-07117ACB2789}">
       <text>
         <r>
@@ -1197,7 +1211,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1929" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1740,7 +1754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:BK34"/>
+  <dimension ref="A1:BL34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1760,16 +1774,16 @@
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
     <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="54" max="61" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="62" max="63" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="62" max="64" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="BK1">
-        <f>COUNTA(BK4:BK34)</f>
+    <row r="1" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BL1">
+        <f>COUNTA(BL4:BL34)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:63" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:64" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1959,8 +1973,11 @@
       <c r="BK3" s="5">
         <v>45089</v>
       </c>
+      <c r="BL3" s="5">
+        <v>45090</v>
+      </c>
     </row>
-    <row r="4" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2150,8 +2167,11 @@
       <c r="BK4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2341,8 +2361,11 @@
       <c r="BK5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2532,8 +2555,11 @@
       <c r="BK6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2723,8 +2749,11 @@
       <c r="BK7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2914,8 +2943,11 @@
       <c r="BK8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -3105,8 +3137,11 @@
       <c r="BK9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -3296,8 +3331,11 @@
       <c r="BK10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -3487,8 +3525,11 @@
       <c r="BK11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -3678,8 +3719,11 @@
       <c r="BK12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -3869,8 +3913,11 @@
       <c r="BK13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -4060,8 +4107,11 @@
       <c r="BK14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -4251,8 +4301,11 @@
       <c r="BK15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -4442,8 +4495,11 @@
       <c r="BK16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -4633,8 +4689,11 @@
       <c r="BK17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -4824,8 +4883,11 @@
       <c r="BK18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -5015,8 +5077,11 @@
       <c r="BK19" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="BL19" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="20" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -5206,8 +5271,11 @@
       <c r="BK20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -5397,8 +5465,11 @@
       <c r="BK21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -5588,8 +5659,11 @@
       <c r="BK22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -5779,8 +5853,11 @@
       <c r="BK23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -5970,8 +6047,11 @@
       <c r="BK24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -6161,8 +6241,11 @@
       <c r="BK25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -6352,8 +6435,11 @@
       <c r="BK26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -6543,8 +6629,11 @@
       <c r="BK27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -6734,8 +6823,11 @@
       <c r="BK28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -6925,8 +7017,11 @@
       <c r="BK29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -7116,8 +7211,11 @@
       <c r="BK30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -7307,8 +7405,11 @@
       <c r="BK31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -7498,8 +7599,11 @@
       <c r="BK32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -7689,8 +7793,11 @@
       <c r="BK33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BL33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -7878,6 +7985,9 @@
         <v>4</v>
       </c>
       <c r="BK34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BL34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44064D41-A950-4D3D-89A3-2F31593C932A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB2E7C2-9322-4D9C-8A11-CA880244E60A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1211,7 +1211,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1929" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1754,7 +1754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:BL34"/>
+  <dimension ref="A1:BM34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1774,16 +1774,16 @@
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
     <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="54" max="61" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="62" max="64" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="62" max="65" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="BL1">
-        <f>COUNTA(BL4:BL34)</f>
+    <row r="1" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="BM1">
+        <f>COUNTA(BM4:BM34)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:64" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:65" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1976,8 +1976,11 @@
       <c r="BL3" s="5">
         <v>45090</v>
       </c>
+      <c r="BM3" s="5">
+        <v>45091</v>
+      </c>
     </row>
-    <row r="4" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2170,8 +2173,11 @@
       <c r="BL4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2364,8 +2370,11 @@
       <c r="BL5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2558,8 +2567,11 @@
       <c r="BL6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2752,8 +2764,11 @@
       <c r="BL7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2946,8 +2961,11 @@
       <c r="BL8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -3140,8 +3158,11 @@
       <c r="BL9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -3334,8 +3355,11 @@
       <c r="BL10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -3528,8 +3552,11 @@
       <c r="BL11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -3722,8 +3749,11 @@
       <c r="BL12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -3916,8 +3946,11 @@
       <c r="BL13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -4110,8 +4143,11 @@
       <c r="BL14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -4304,8 +4340,11 @@
       <c r="BL15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -4498,8 +4537,11 @@
       <c r="BL16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -4692,8 +4734,11 @@
       <c r="BL17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -4886,8 +4931,11 @@
       <c r="BL18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -5080,8 +5128,11 @@
       <c r="BL19" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="BM19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -5274,8 +5325,11 @@
       <c r="BL20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -5468,8 +5522,11 @@
       <c r="BL21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -5662,8 +5719,11 @@
       <c r="BL22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -5856,8 +5916,11 @@
       <c r="BL23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -6050,8 +6113,11 @@
       <c r="BL24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -6244,8 +6310,11 @@
       <c r="BL25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -6438,8 +6507,11 @@
       <c r="BL26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -6632,8 +6704,11 @@
       <c r="BL27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -6826,8 +6901,11 @@
       <c r="BL28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -7020,8 +7098,11 @@
       <c r="BL29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -7214,8 +7295,11 @@
       <c r="BL30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -7408,8 +7492,11 @@
       <c r="BL31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -7602,8 +7689,11 @@
       <c r="BL32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -7796,8 +7886,11 @@
       <c r="BL33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BM33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:64" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -7988,6 +8081,9 @@
         <v>4</v>
       </c>
       <c r="BL34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BM34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB2E7C2-9322-4D9C-8A11-CA880244E60A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0848D095-11C0-40D3-B35E-9521CC121657}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,6 +53,21 @@
         </r>
       </text>
     </comment>
+    <comment ref="BP6" authorId="0" shapeId="0" xr:uid="{FD55F6C6-469C-4178-A7B6-73CAAEE2A66E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:15
+Forgot ID card and went back</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="N7" authorId="0" shapeId="0" xr:uid="{F6F4F720-DA46-4DC0-8124-2D3953156CC6}">
       <text>
         <r>
@@ -533,6 +548,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BO18" authorId="0" shapeId="0" xr:uid="{1C71F9F4-12AE-4E33-AE32-4180EF4F2C98}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="BJ19" authorId="0" shapeId="0" xr:uid="{48F35BF0-9CB9-4D81-AF45-B901F733BC15}">
       <text>
         <r>
@@ -1094,6 +1123,21 @@
         </r>
       </text>
     </comment>
+    <comment ref="BP30" authorId="0" shapeId="0" xr:uid="{22271C8A-B591-41BF-BBDC-520181D22DE3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">09:13
+Sick. </t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z32" authorId="0" shapeId="0" xr:uid="{59E0B9C2-F2EA-4082-81B3-59239B204C71}">
       <text>
         <r>
@@ -1175,6 +1219,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:03</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BO32" authorId="0" shapeId="0" xr:uid="{136DF9C4-AE20-4CE5-82A1-B3BF5B5F2BFA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:02</t>
         </r>
       </text>
     </comment>
@@ -1211,7 +1269,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1409,7 +1467,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1508,11 +1566,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1537,6 +1606,9 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1754,7 +1826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:BM34"/>
+  <dimension ref="A1:BQ34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1774,16 +1846,16 @@
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
     <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="54" max="61" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="62" max="65" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="62" max="68" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="BM1">
-        <f>COUNTA(BM4:BM34)</f>
+    <row r="1" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BP1">
+        <f>COUNTA(BP4:BP34)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:65" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:69" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1979,8 +2051,17 @@
       <c r="BM3" s="5">
         <v>45091</v>
       </c>
+      <c r="BN3" s="5">
+        <v>45092</v>
+      </c>
+      <c r="BO3" s="5">
+        <v>45093</v>
+      </c>
+      <c r="BP3" s="5">
+        <v>45094</v>
+      </c>
     </row>
-    <row r="4" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2176,8 +2257,17 @@
       <c r="BM4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2373,8 +2463,17 @@
       <c r="BM5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2570,8 +2669,18 @@
       <c r="BM6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BQ6" s="12"/>
     </row>
-    <row r="7" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2767,8 +2876,17 @@
       <c r="BM7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2964,8 +3082,17 @@
       <c r="BM8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -3161,8 +3288,17 @@
       <c r="BM9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -3358,8 +3494,17 @@
       <c r="BM10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -3555,8 +3700,17 @@
       <c r="BM11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -3752,8 +3906,17 @@
       <c r="BM12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -3949,8 +4112,17 @@
       <c r="BM13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -4146,8 +4318,17 @@
       <c r="BM14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -4343,8 +4524,17 @@
       <c r="BM15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -4540,8 +4730,17 @@
       <c r="BM16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -4737,8 +4936,17 @@
       <c r="BM17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -4934,8 +5142,17 @@
       <c r="BM18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -5131,8 +5348,17 @@
       <c r="BM19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -5328,8 +5554,17 @@
       <c r="BM20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -5525,8 +5760,17 @@
       <c r="BM21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -5722,8 +5966,17 @@
       <c r="BM22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -5919,8 +6172,17 @@
       <c r="BM23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -6116,8 +6378,17 @@
       <c r="BM24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -6313,8 +6584,17 @@
       <c r="BM25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -6510,8 +6790,17 @@
       <c r="BM26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -6707,8 +6996,17 @@
       <c r="BM27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -6904,8 +7202,17 @@
       <c r="BM28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN28" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO28" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -7101,8 +7408,17 @@
       <c r="BM29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -7298,8 +7614,18 @@
       <c r="BM30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BQ30" s="12"/>
     </row>
-    <row r="31" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -7495,8 +7821,17 @@
       <c r="BM31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -7692,8 +8027,17 @@
       <c r="BM32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -7889,8 +8233,17 @@
       <c r="BM33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BN33" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO33" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:65" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -8084,6 +8437,15 @@
         <v>4</v>
       </c>
       <c r="BM34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BN34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0848D095-11C0-40D3-B35E-9521CC121657}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A85AD67-9641-48D8-B68F-D1B815C54058}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -168,6 +168,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BQ9" authorId="0" shapeId="0" xr:uid="{58F9013A-5E17-44CE-A1B7-B23E2E98B046}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AB10" authorId="0" shapeId="0" xr:uid="{3E374D75-3895-49F1-B346-BE43AE381426}">
       <text>
         <r>
@@ -249,6 +263,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:01</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BQ10" authorId="0" shapeId="0" xr:uid="{14D1A9BB-1E8E-4A78-BC12-13282ECB96C6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04</t>
         </r>
       </text>
     </comment>
@@ -702,6 +730,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="BQ20" authorId="0" shapeId="0" xr:uid="{27B76FF6-C387-4540-9AEE-E24A02AAEF0F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BQ21" authorId="0" shapeId="0" xr:uid="{257558CA-95A4-47AA-ABD5-01685BE342F1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z22" authorId="0" shapeId="0" xr:uid="{DDD8C7AD-47C9-4E11-8FE8-07117ACB2789}">
       <text>
         <r>
@@ -811,6 +867,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:03</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BQ23" authorId="0" shapeId="0" xr:uid="{DCB07AC3-9CBF-4ECD-B9FF-12883BEBA30D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:01</t>
         </r>
       </text>
     </comment>
@@ -1269,7 +1339,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1467,7 +1537,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1566,22 +1636,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1606,9 +1665,6 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1846,12 +1902,12 @@
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
     <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="54" max="61" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="62" max="68" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="62" max="69" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="BP1">
-        <f>COUNTA(BP4:BP34)</f>
+      <c r="BQ1">
+        <f>COUNTA(BQ4:BQ34)</f>
         <v>31</v>
       </c>
     </row>
@@ -2060,6 +2116,9 @@
       <c r="BP3" s="5">
         <v>45094</v>
       </c>
+      <c r="BQ3" s="5">
+        <v>45096</v>
+      </c>
     </row>
     <row r="4" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
@@ -2266,6 +2325,9 @@
       <c r="BP4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
@@ -2472,6 +2534,9 @@
       <c r="BP5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
@@ -2678,7 +2743,9 @@
       <c r="BP6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="BQ6" s="12"/>
+      <c r="BQ6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
@@ -2883,6 +2950,9 @@
         <v>4</v>
       </c>
       <c r="BP7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BQ7" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3091,6 +3161,9 @@
       <c r="BP8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
@@ -3297,6 +3370,9 @@
       <c r="BP9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
@@ -3503,6 +3579,9 @@
       <c r="BP10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
@@ -3709,6 +3788,9 @@
       <c r="BP11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
@@ -3915,6 +3997,9 @@
       <c r="BP12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
@@ -4121,6 +4206,9 @@
       <c r="BP13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
@@ -4327,6 +4415,9 @@
       <c r="BP14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
@@ -4533,6 +4624,9 @@
       <c r="BP15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
@@ -4739,6 +4833,9 @@
       <c r="BP16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
@@ -4945,6 +5042,9 @@
       <c r="BP17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
@@ -5151,6 +5251,9 @@
       <c r="BP18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="19" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
@@ -5357,6 +5460,9 @@
       <c r="BP19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="20" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
@@ -5563,6 +5669,9 @@
       <c r="BP20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
@@ -5769,6 +5878,9 @@
       <c r="BP21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
@@ -5975,6 +6087,9 @@
       <c r="BP22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
@@ -6181,6 +6296,9 @@
       <c r="BP23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="24" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
@@ -6387,6 +6505,9 @@
       <c r="BP24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="25" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
@@ -6593,6 +6714,9 @@
       <c r="BP25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="26" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
@@ -6799,6 +6923,9 @@
       <c r="BP26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="27" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
@@ -7005,6 +7132,9 @@
       <c r="BP27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
@@ -7211,6 +7341,9 @@
       <c r="BP28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="29" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
@@ -7417,6 +7550,9 @@
       <c r="BP29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="30" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
@@ -7623,7 +7759,9 @@
       <c r="BP30" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="BQ30" s="12"/>
+      <c r="BQ30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
@@ -7830,6 +7968,9 @@
       <c r="BP31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ31" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="32" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
@@ -8036,8 +8177,11 @@
       <c r="BP32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -8242,8 +8386,11 @@
       <c r="BP33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BQ33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -8446,6 +8593,9 @@
         <v>4</v>
       </c>
       <c r="BP34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BQ34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A85AD67-9641-48D8-B68F-D1B815C54058}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3CAC27-4256-413D-ACE7-0F331EF5429A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -744,6 +744,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BS20" authorId="0" shapeId="0" xr:uid="{9FDFE411-681D-4C60-B5FE-E69E26D6177E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="BQ21" authorId="0" shapeId="0" xr:uid="{257558CA-95A4-47AA-ABD5-01685BE342F1}">
       <text>
         <r>
@@ -966,6 +980,20 @@
           </rPr>
           <t>09:04
 He came in rain with full of water. But still tried to reach on time</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BS24" authorId="0" shapeId="0" xr:uid="{8AA90C7C-0645-4D36-BF6C-A52F6C67C03A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:04</t>
         </r>
       </text>
     </comment>
@@ -1339,7 +1367,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="44">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1882,7 +1910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:BQ34"/>
+  <dimension ref="A1:BS34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1902,16 +1930,16 @@
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
     <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="54" max="61" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="62" max="69" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="62" max="71" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="BQ1">
-        <f>COUNTA(BQ4:BQ34)</f>
+    <row r="1" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BS1">
+        <f>COUNTA(BS4:BS34)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:69" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:71" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -2119,8 +2147,14 @@
       <c r="BQ3" s="5">
         <v>45096</v>
       </c>
+      <c r="BR3" s="5">
+        <v>45097</v>
+      </c>
+      <c r="BS3" s="5">
+        <v>45098</v>
+      </c>
     </row>
-    <row r="4" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2328,8 +2362,14 @@
       <c r="BQ4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2537,8 +2577,14 @@
       <c r="BQ5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2746,8 +2792,14 @@
       <c r="BQ6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2955,8 +3007,14 @@
       <c r="BQ7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -3164,8 +3222,14 @@
       <c r="BQ8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -3373,8 +3437,14 @@
       <c r="BQ9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -3582,8 +3652,14 @@
       <c r="BQ10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -3791,8 +3867,14 @@
       <c r="BQ11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -4000,8 +4082,14 @@
       <c r="BQ12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -4209,8 +4297,14 @@
       <c r="BQ13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -4418,8 +4512,14 @@
       <c r="BQ14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -4627,8 +4727,14 @@
       <c r="BQ15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -4836,8 +4942,14 @@
       <c r="BQ16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -5045,8 +5157,14 @@
       <c r="BQ17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -5254,8 +5372,14 @@
       <c r="BQ18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -5463,8 +5587,14 @@
       <c r="BQ19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -5672,8 +5802,14 @@
       <c r="BQ20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -5881,8 +6017,14 @@
       <c r="BQ21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -6090,8 +6232,14 @@
       <c r="BQ22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -6299,8 +6447,14 @@
       <c r="BQ23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -6508,8 +6662,14 @@
       <c r="BQ24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -6717,8 +6877,14 @@
       <c r="BQ25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -6926,8 +7092,14 @@
       <c r="BQ26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -7135,8 +7307,14 @@
       <c r="BQ27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -7344,8 +7522,14 @@
       <c r="BQ28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR28" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -7553,8 +7737,14 @@
       <c r="BQ29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -7762,8 +7952,14 @@
       <c r="BQ30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -7971,8 +8167,14 @@
       <c r="BQ31" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="BR31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -8180,8 +8382,14 @@
       <c r="BQ32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -8389,8 +8597,14 @@
       <c r="BQ33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BR33" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:69" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -8596,6 +8810,12 @@
         <v>4</v>
       </c>
       <c r="BQ34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BR34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BS34" s="8" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Attendance_UST batch1 Jag.xlsx
+++ b/Attendance_UST batch1 Jag.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3CAC27-4256-413D-ACE7-0F331EF5429A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E296816-8F0C-478D-88ED-344F258C1260}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="2" r:id="rId1"/>
+    <sheet name="New_Attendance" sheetId="3" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">New_Attendance!$A$3:$I$33</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
@@ -758,6 +762,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="BT20" authorId="0" shapeId="0" xr:uid="{857F75F2-E490-46C2-93EF-93970865CC68}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:05</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="BQ21" authorId="0" shapeId="0" xr:uid="{257558CA-95A4-47AA-ABD5-01685BE342F1}">
       <text>
         <r>
@@ -994,6 +1012,20 @@
             <charset val="1"/>
           </rPr>
           <t>09:04</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BU24" authorId="0" shapeId="0" xr:uid="{ACC55D39-370F-4BDA-AC63-E93DC9E81850}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>09:03</t>
         </r>
       </text>
     </comment>
@@ -1367,7 +1399,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="62">
   <si>
     <t>Neethu Nelliparambil Rathimohan</t>
   </si>
@@ -1500,6 +1532,60 @@
   <si>
     <t>A</t>
   </si>
+  <si>
+    <t>Sidharth p k</t>
+  </si>
+  <si>
+    <t>Abitha Baby</t>
+  </si>
+  <si>
+    <t>Tony Kurian</t>
+  </si>
+  <si>
+    <t>Amal Thekkel Sobhanakumari</t>
+  </si>
+  <si>
+    <t>Akhila Madhavan</t>
+  </si>
+  <si>
+    <t>Ansiya Salam</t>
+  </si>
+  <si>
+    <t>Ashna Shamsudeen</t>
+  </si>
+  <si>
+    <t>Dhanya Kollanoor Chery</t>
+  </si>
+  <si>
+    <t>Charusree K</t>
+  </si>
+  <si>
+    <t>Joseph James</t>
+  </si>
+  <si>
+    <t>Divya Sobha Kumari Nair</t>
+  </si>
+  <si>
+    <t>SHAFNA K M</t>
+  </si>
+  <si>
+    <t>Yadukrishnan J</t>
+  </si>
+  <si>
+    <t>LEKSHMY M</t>
+  </si>
+  <si>
+    <t>batch 2</t>
+  </si>
+  <si>
+    <t>Jagadeeswaran R</t>
+  </si>
+  <si>
+    <t>batch 1</t>
+  </si>
+  <si>
+    <t>team #</t>
+  </si>
 </sst>
 </file>
 
@@ -1508,7 +1594,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1556,13 +1642,40 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="8">
@@ -1668,7 +1781,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1694,6 +1807,16 @@
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1910,7 +2033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1CE229-5C7B-4A55-BA1C-7AC460CD1DB9}">
-  <dimension ref="A1:BS34"/>
+  <dimension ref="A1:BU34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1930,16 +2053,16 @@
     <col min="38" max="38" width="11.77734375" customWidth="1"/>
     <col min="39" max="53" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="54" max="61" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="62" max="71" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="62" max="73" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="BS1">
-        <f>COUNTA(BS4:BS34)</f>
+    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BU1">
+        <f>COUNTA(BU4:BU34)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:71" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:73" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -2153,8 +2276,14 @@
       <c r="BS3" s="5">
         <v>45098</v>
       </c>
+      <c r="BT3" s="5">
+        <v>45099</v>
+      </c>
+      <c r="BU3" s="5">
+        <v>45100</v>
+      </c>
     </row>
-    <row r="4" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2368,8 +2497,14 @@
       <c r="BS4" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU4" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2583,8 +2718,14 @@
       <c r="BS5" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU5" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2798,8 +2939,14 @@
       <c r="BS6" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU6" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -3013,8 +3160,14 @@
       <c r="BS7" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU7" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -3228,8 +3381,14 @@
       <c r="BS8" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU8" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -3443,8 +3602,14 @@
       <c r="BS9" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU9" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -3658,8 +3823,14 @@
       <c r="BS10" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU10" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -3873,8 +4044,14 @@
       <c r="BS11" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU11" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -4088,8 +4265,14 @@
       <c r="BS12" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU12" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -4303,8 +4486,14 @@
       <c r="BS13" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU13" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -4518,8 +4707,14 @@
       <c r="BS14" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU14" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -4733,8 +4928,14 @@
       <c r="BS15" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU15" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -4948,8 +5149,14 @@
       <c r="BS16" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU16" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -5163,8 +5370,14 @@
       <c r="BS17" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU17" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -5378,8 +5591,14 @@
       <c r="BS18" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU18" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -5593,8 +5812,14 @@
       <c r="BS19" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU19" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -5808,8 +6033,14 @@
       <c r="BS20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU20" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -6023,8 +6254,14 @@
       <c r="BS21" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU21" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -6238,8 +6475,14 @@
       <c r="BS22" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU22" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -6453,8 +6696,14 @@
       <c r="BS23" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU23" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -6668,8 +6917,14 @@
       <c r="BS24" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU24" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -6883,8 +7138,14 @@
       <c r="BS25" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU25" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -7098,8 +7359,14 @@
       <c r="BS26" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU26" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -7313,8 +7580,14 @@
       <c r="BS27" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU27" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -7528,8 +7801,14 @@
       <c r="BS28" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT28" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU28" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="29" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -7743,8 +8022,14 @@
       <c r="BS29" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU29" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -7958,8 +8243,14 @@
       <c r="BS30" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU30" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="31" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -8173,8 +8464,14 @@
       <c r="BS31" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU31" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="32" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -8388,8 +8685,14 @@
       <c r="BS32" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU32" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -8603,8 +8906,14 @@
       <c r="BS33" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="BT33" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU33" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -8816,6 +9125,12 @@
         <v>4</v>
       </c>
       <c r="BS34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BT34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU34" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8824,4 +9139,875 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D660CE97-36A9-4E75-AAAB-545234A053BC}">
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I1">
+        <f>COUNTA(I4:I33)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="5">
+        <v>45099</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
+        <v>1</v>
+      </c>
+      <c r="B4" s="14">
+        <v>248764</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="15">
+        <v>1</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="12">
+        <v>2</v>
+      </c>
+      <c r="B5" s="14">
+        <v>249440</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="15">
+        <v>1</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="12"/>
+    </row>
+    <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14">
+        <v>248761</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="15">
+        <v>1</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="12">
+        <v>4</v>
+      </c>
+      <c r="B7" s="14">
+        <v>248742</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="15">
+        <v>3</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="12"/>
+    </row>
+    <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="12">
+        <v>5</v>
+      </c>
+      <c r="B8" s="14">
+        <v>248753</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="15">
+        <v>3</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="12">
+        <v>6</v>
+      </c>
+      <c r="B9" s="14">
+        <v>248803</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="15">
+        <v>3</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="12"/>
+    </row>
+    <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="12">
+        <v>7</v>
+      </c>
+      <c r="B10" s="14">
+        <v>249529</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="15">
+        <v>5</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="12">
+        <v>8</v>
+      </c>
+      <c r="B11" s="14">
+        <v>248769</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="15">
+        <v>5</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="12"/>
+    </row>
+    <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="12">
+        <v>9</v>
+      </c>
+      <c r="B12" s="14">
+        <v>248740</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="15">
+        <v>5</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="12">
+        <v>10</v>
+      </c>
+      <c r="B13" s="14">
+        <v>248775</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="15">
+        <v>7</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="12"/>
+    </row>
+    <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="12">
+        <v>11</v>
+      </c>
+      <c r="B14" s="14">
+        <v>248799</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="15">
+        <v>7</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="12"/>
+    </row>
+    <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="12">
+        <v>12</v>
+      </c>
+      <c r="B15" s="14">
+        <v>248819</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="15">
+        <v>7</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="12"/>
+    </row>
+    <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="12">
+        <v>13</v>
+      </c>
+      <c r="B16" s="14">
+        <v>248735</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="15">
+        <v>9</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="12"/>
+    </row>
+    <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="12">
+        <v>14</v>
+      </c>
+      <c r="B17" s="14">
+        <v>248789</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="15">
+        <v>9</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="12"/>
+    </row>
+    <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="12">
+        <v>15</v>
+      </c>
+      <c r="B18" s="14">
+        <v>248765</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="15">
+        <v>9</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="12"/>
+    </row>
+    <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="12">
+        <v>16</v>
+      </c>
+      <c r="B19" s="14">
+        <v>248723</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="15">
+        <v>11</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I19" s="12"/>
+    </row>
+    <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="12">
+        <v>17</v>
+      </c>
+      <c r="B20" s="14">
+        <v>248739</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="15">
+        <v>11</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="12"/>
+    </row>
+    <row r="21" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="12">
+        <v>18</v>
+      </c>
+      <c r="B21" s="14">
+        <v>249416</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="15">
+        <v>11</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="12"/>
+    </row>
+    <row r="22" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="12">
+        <v>19</v>
+      </c>
+      <c r="B22" s="14">
+        <v>248731</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="15">
+        <v>14</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="12"/>
+    </row>
+    <row r="23" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="12">
+        <v>20</v>
+      </c>
+      <c r="B23" s="14">
+        <v>248780</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="15">
+        <v>14</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="12"/>
+    </row>
+    <row r="24" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="12">
+        <v>21</v>
+      </c>
+      <c r="B24" s="14">
+        <v>249175</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="15">
+        <v>14</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="12"/>
+    </row>
+    <row r="25" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="12">
+        <v>22</v>
+      </c>
+      <c r="B25" s="14">
+        <v>248729</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25" s="15">
+        <v>16</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="12"/>
+    </row>
+    <row r="26" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="12">
+        <v>23</v>
+      </c>
+      <c r="B26" s="14">
+        <v>249408</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" s="15">
+        <v>16</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="12"/>
+    </row>
+    <row r="27" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="12">
+        <v>24</v>
+      </c>
+      <c r="B27" s="14">
+        <v>248771</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F27" s="15">
+        <v>16</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="12"/>
+    </row>
+    <row r="28" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="12">
+        <v>25</v>
+      </c>
+      <c r="B28" s="14">
+        <v>248722</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" s="15">
+        <v>18</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I28" s="12"/>
+    </row>
+    <row r="29" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="12">
+        <v>26</v>
+      </c>
+      <c r="B29" s="14">
+        <v>248774</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="15">
+        <v>18</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="12"/>
+    </row>
+    <row r="30" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="12">
+        <v>27</v>
+      </c>
+      <c r="B30" s="14">
+        <v>248777</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30" s="15">
+        <v>18</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I30" s="12"/>
+    </row>
+    <row r="31" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="12">
+        <v>28</v>
+      </c>
+      <c r="B31" s="14">
+        <v>248875</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F31" s="15">
+        <v>20</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="12"/>
+    </row>
+    <row r="32" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="12">
+        <v>29</v>
+      </c>
+      <c r="B32" s="14">
+        <v>248762</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F32" s="15">
+        <v>20</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="12"/>
+    </row>
+    <row r="33" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="12">
+        <v>30</v>
+      </c>
+      <c r="B33" s="14">
+        <v>249389</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F33" s="15">
+        <v>20</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="12"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:I33">
+    <sortCondition ref="F4:F33"/>
+    <sortCondition ref="C4:C33"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>